--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>

--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -1693,7 +1693,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>

--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -1237,7 +1237,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>

--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L222"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>שלומי ימין - מסתובב ברחובות</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410584&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Madonna</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>שלומי ימין - מסתובב ברחובות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>רגב קהלני - כוסות של יין אדום</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410583&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Freya Ridings</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>רגב קהלני - כוסות של יין אדום</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>קיזל - אמת חיי</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410582&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Celine Dion</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>קיזל - אמת חיי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>מיכאל יגודאייב - הנעליים שנשארו</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410579&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Peter Gabriel</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>מיכאל יגודאייב - הנעליים שנשארו</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>ליאור קקון &amp; שקד סולומון - שבועה באוקטובר</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410578&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>ליאור קקון &amp; שקד סולומון - שבועה באוקטובר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>להקת פיקוד דרום &amp; חני נחמיאס &amp; אביבה אבידן - פרחים בקנה 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410577&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Jessie Ware</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>להקת פיקוד דרום &amp; חני נחמיאס &amp; אביבה אבידן - פרחים בקנה 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>טלי רבקה סימן טוב - חזרתי 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410576&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Kid LAROI.</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>טלי רבקה סימן טוב - חזרתי 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>זיו אלול - קום לביא</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410575&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>ERNEST</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>זיו אלול - קום לביא</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>אייל אלבז - שיר ליואב</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410574&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>אייל אלבז - שיר ליואב</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>אבי אילסון - בזכותם - גרסה ווקאלית</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410573&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dean Lewis</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>אבי אילסון - בזכותם - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>האחים בכר - נשאר הגעגוע - גרסה ווקאלית</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410572&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Bella White</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,36 +849,36 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>האחים בכר - נשאר הגעגוע - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>אליה לוי - אהבת השם</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410571&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Kip Moore</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,36 +887,36 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>אליה לוי - אהבת השם</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>אליאור מדר - שלוש מילים קטנות</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410570&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Olivia Rodrigo</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,36 +925,36 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>אליאור מדר - שלוש מילים קטנות</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>אבי אילסון &amp; מוטי איידנסון - דיבור של הלב - גרסה ווקאלית</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410569&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Ben Gallaher</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,36 +963,36 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>אבי אילסון &amp; מוטי איידנסון - דיבור של הלב - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410585&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Reservoir Recordings</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,36 +1001,36 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>קורין גמליאל - יהיה בסדר קאבר</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410581&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Johnny Orlando</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,36 +1039,36 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>קורין גמליאל - יהיה בסדר קאבר</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410580&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Tyla</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Danna</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Lana Del Rey</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Loreen</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Cannons</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Tenille Townes</v>
+        <v>Beck</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Danna</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>OneRepublic</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The Revivalists</v>
+        <v>Beck</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>James Smith</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Holly Humberstone</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Ava Max</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>John Summit</v>
+        <v>Madonna</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ava Max</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Danna</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Conan Gray</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>TemplesOfficial</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Laufey</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>bleachers</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Nothing But Thieves</v>
+        <v>ERNEST</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>LANY</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Bella White</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>florencemachine</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Scorpions</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Holly Humberstone</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>HAUSER</v>
+        <v>Tyla</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Mae Muller</v>
+        <v>Loreen</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Dead Pony</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>kenzie - where do we go</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>kenzie</v>
+        <v>Danna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Foo Fighters</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Laufey</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Ella Langley</v>
+        <v>James Smith</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Mei Semones</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Evanescence</v>
+        <v>Ava Max</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>elijah woods</v>
+        <v>John Summit</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>colby!</v>
+        <v>Ava Max</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Chainsmokers</v>
+        <v>Danna</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>aron!</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Owen Riegling</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Laufey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Teddy Swims</v>
+        <v>bleachers</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>LANY</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Sunday (1994)</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Freya Skye</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Bryan Adams</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>We Three</v>
+        <v>florencemachine</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Scorpions</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Bebe Rexha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>The Lemon Twigs</v>
+        <v>HAUSER</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>METTE</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Saint Harison</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>NewDad</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Danna</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>florencemachine</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>HYBE LABELS</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Kungs</v>
+        <v>kenzie</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Charlie Puth</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Madison Cunningham</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armin van Buuren</v>
+        <v>Evanescence</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>elijah woods</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Nothing But Thieves</v>
+        <v>colby!</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Ocean Alley</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>RAYE</v>
+        <v>aron!</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Take That</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Armik</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Switchfoot</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Peter Gabriel</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Sarah Julia</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Chris Norman</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Alan Walker</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Charlie Puth</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Miley Cyrus</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,3926 +4231,4610 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Better</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>U</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Baauer</v>
+        <v>We Three</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Better - Baauer</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>drop dead</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:44</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>drop dead - Olivia Rodrigo</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>I Feel So Free</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>CONFESSIONS II</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>5:03</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>I Feel So Free - Madonna</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>First Light</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>First Light - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:24</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Lana Del Rey</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Focu 'Ranni</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>ROSALÍA</v>
+        <v>METTE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Middle of Nowhere</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Rackies</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:53</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Sexyy Red</v>
+        <v>NewDad</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:33</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Tyla</v>
+        <v>Danna</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Potential</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Potential - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>4:02</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>sombr</v>
+        <v>florencemachine</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Potential - sombr</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Pa' la seca</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Maluma</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Nightlife</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>Honey Dijon</v>
+        <v>Kungs</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Ride Lonesome</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>4:32</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Beck</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BIAF &lt;3</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>Young Miko</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:14</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>DANNA</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>i just get worse</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>i just get worse - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G116" t="str">
-        <v>3:25</v>
+        <v/>
       </c>
       <c r="H116" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G117" t="str">
-        <v>3:23</v>
+        <v/>
       </c>
       <c r="H117" t="str">
-        <v>John Summit</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Side Effects</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G118" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Numb</v>
+        <v>earth is turning</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Numb - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G119" t="str">
-        <v>2:34</v>
+        <v>4:49</v>
       </c>
       <c r="H119" t="str">
-        <v>JT</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L119" t="str">
-        <v>Numb - JT</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>drop dead</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G120" t="str">
-        <v>3:05</v>
+        <v>3:44</v>
       </c>
       <c r="H120" t="str">
-        <v>Labrinth</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L120" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G121" t="str">
-        <v>2:47</v>
+        <v>5:03</v>
       </c>
       <c r="H121" t="str">
-        <v>Miley Cyrus</v>
+        <v>Madonna</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L121" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>My Way</v>
+        <v>First Light</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>My Way - Single</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>4:02</v>
+        <v>3:24</v>
       </c>
       <c r="H122" t="str">
-        <v>Riley Green</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L122" t="str">
-        <v>My Way - Riley Green</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Ache</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Bloom - Single</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G123" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H123" t="str">
-        <v>Not for Radio</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L123" t="str">
-        <v>Ache - Not for Radio</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Cut Ties</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G124" t="str">
-        <v>4:09</v>
+        <v>2:36</v>
       </c>
       <c r="H124" t="str">
-        <v>Anne Hathaway</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L124" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Rackies</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G125" t="str">
-        <v>2:13</v>
+        <v>2:53</v>
       </c>
       <c r="H125" t="str">
-        <v>Slayyyter</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L125" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Nine Inch Noize</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:57</v>
+        <v>3:33</v>
       </c>
       <c r="H126" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Tyla</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L126" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Boots on the Ground</v>
+        <v>Potential</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:21</v>
+        <v>4:02</v>
       </c>
       <c r="H127" t="str">
-        <v>Massive Attack</v>
+        <v>sombr</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L127" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H128" t="str">
-        <v>Demi Lovato</v>
+        <v>Maluma</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L128" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I CONDEMN</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G129" t="str">
-        <v>2:22</v>
+        <v>3:32</v>
       </c>
       <c r="H129" t="str">
-        <v>The Kid LAROI</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L129" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Wannabeher</v>
+        <v>Better</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Dancing On The Wall</v>
+        <v>U</v>
       </c>
       <c r="G130" t="str">
-        <v>2:34</v>
+        <v>3:50</v>
       </c>
       <c r="H130" t="str">
-        <v>MUNA</v>
+        <v>Baauer</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L130" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Superbloom</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Superbloom</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:11</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Jessie Ware</v>
+        <v>Young Miko</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L131" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Chairwoman Park</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>1:40</v>
+        <v>4:32</v>
       </c>
       <c r="H132" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Beck</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L132" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Make You Move</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Make You Move - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>2:24</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Dillon Francis</v>
+        <v>DANNA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L133" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>FERRARI</v>
+        <v>i just get worse</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FERRARI - Single</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:14</v>
+        <v>3:25</v>
       </c>
       <c r="H134" t="str">
-        <v>Clave Especial</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L134" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Por Ella</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G135" t="str">
-        <v>3:01</v>
+        <v>3:23</v>
       </c>
       <c r="H135" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>John Summit</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L135" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Stick With You</v>
+        <v>Side Effects</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G136" t="str">
-        <v>2:33</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>ZAYN</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L136" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>KGB</v>
+        <v>Numb</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>KGB - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:37</v>
+        <v>2:34</v>
       </c>
       <c r="H137" t="str">
-        <v>ADÉLA</v>
+        <v>JT</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L137" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Holly!</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:10</v>
+        <v>3:05</v>
       </c>
       <c r="H138" t="str">
-        <v>The Band CAMINO</v>
+        <v>Labrinth</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L138" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Sunday Again</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H139" t="str">
-        <v>6LACK</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L139" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Move Time</v>
+        <v>My Way</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Move Time - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:39</v>
+        <v>4:02</v>
       </c>
       <c r="H140" t="str">
-        <v>MJ Cole</v>
+        <v>Riley Green</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L140" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>I Want You</v>
+        <v>Ache</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:10</v>
+        <v>4:25</v>
       </c>
       <c r="H141" t="str">
-        <v>Cody Johnson</v>
+        <v>Not-For-Radio</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L141" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Ache - Not-For-Radio</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Straddle Me</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G142" t="str">
-        <v>3:11</v>
+        <v>4:09</v>
       </c>
       <c r="H142" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L142" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ring</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Ring - Single</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:21</v>
+        <v>2:13</v>
       </c>
       <c r="H143" t="str">
-        <v>Queen Naija</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L143" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Wild</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G144" t="str">
-        <v>3:24</v>
+        <v>3:57</v>
       </c>
       <c r="H144" t="str">
-        <v>Ashley McBryde</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L144" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Stay Love</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Survive - EP</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H145" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L145" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Love Me</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Dear God</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H146" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L146" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:02</v>
+        <v>2:22</v>
       </c>
       <c r="H147" t="str">
-        <v>Dean Lewis</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L147" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Balboa Park</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Let It Die Here</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G148" t="str">
-        <v>3:52</v>
+        <v>2:34</v>
       </c>
       <c r="H148" t="str">
-        <v>Linda Perry</v>
+        <v>MUNA</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L148" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The One You Loved</v>
+        <v>Superbloom</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G149" t="str">
-        <v>3:08</v>
+        <v>4:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Kenya Grace</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L149" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Desgraça</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G150" t="str">
-        <v>2:50</v>
+        <v>1:40</v>
       </c>
       <c r="H150" t="str">
-        <v>Anitta</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L150" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Make You Move</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:44</v>
+        <v>2:24</v>
       </c>
       <c r="H151" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L151" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Dansons</v>
+        <v>FERRARI</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Dansons - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:26</v>
+        <v>2:14</v>
       </c>
       <c r="H152" t="str">
-        <v>Céline Dion</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L152" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Por Ella</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:57</v>
+        <v>3:01</v>
       </c>
       <c r="H153" t="str">
-        <v>Trousdale</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L153" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Stick With You</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G154" t="str">
-        <v>5:21</v>
+        <v>2:33</v>
       </c>
       <c r="H154" t="str">
-        <v>This Is Lorelei</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L154" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>KGB</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:49</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Jack Johnson</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L155" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Holly!</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Dream Chaser</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:32</v>
+        <v>3:10</v>
       </c>
       <c r="H156" t="str">
-        <v>Willie Nelson</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L156" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>COME CLOSER</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G157" t="str">
-        <v>7:56</v>
+        <v>3:40</v>
       </c>
       <c r="H157" t="str">
-        <v>TOMORA</v>
+        <v>6LACK</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L157" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Everything U</v>
+        <v>Move Time</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>If This Is It</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:30</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>DJ Seinfeld</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L158" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>If It's Not Love</v>
+        <v>I Want You</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G159" t="str">
-        <v>4:21</v>
+        <v>3:10</v>
       </c>
       <c r="H159" t="str">
-        <v>ZERB</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L159" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Our Last Fight</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>soft pop</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:02</v>
+        <v>3:11</v>
       </c>
       <c r="H160" t="str">
-        <v>Amy Shark</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L160" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Ring</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Subtronics</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L161" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>The Perfect One</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Wild</v>
       </c>
       <c r="G162" t="str">
-        <v>2:56</v>
+        <v>3:24</v>
       </c>
       <c r="H162" t="str">
-        <v>rjtheweirdo</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L162" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Outside</v>
+        <v>Stay Love</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Outside - Single</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:15</v>
+        <v>3:26</v>
       </c>
       <c r="H163" t="str">
-        <v>Inayah</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L163" t="str">
-        <v>Outside - Inayah</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Love Me</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G164" t="str">
-        <v>2:25</v>
+        <v>4:23</v>
       </c>
       <c r="H164" t="str">
-        <v>Jessie Reyez</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L164" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H165" t="str">
-        <v>Max McNown</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L165" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Heart Stop</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Get It Honest</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G166" t="str">
-        <v>4:19</v>
+        <v>3:52</v>
       </c>
       <c r="H166" t="str">
-        <v>The Revivalists</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L166" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Don't Ask Me</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:14</v>
+        <v>3:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Vincent Mason</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L167" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>OSADÍA</v>
+        <v>Desgraça</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>OSADÍA - Single</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G168" t="str">
-        <v>3:26</v>
+        <v>2:50</v>
       </c>
       <c r="H168" t="str">
-        <v>Eden Muñoz</v>
+        <v>Anitta</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L168" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Deep Water</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Deep Water - EP</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G169" t="str">
-        <v>2:33</v>
+        <v>2:44</v>
       </c>
       <c r="H169" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L169" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Time Is A Thief</v>
+        <v>Dansons</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Deep Blue</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H170" t="str">
-        <v>ERNEST</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L170" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>1:58</v>
+        <v>2:57</v>
       </c>
       <c r="H171" t="str">
-        <v>Marca MP</v>
+        <v>Trousdale</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L171" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Price of Love</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G172" t="str">
-        <v>3:29</v>
+        <v>5:21</v>
       </c>
       <c r="H172" t="str">
-        <v>Benny G</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L172" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Las Flores</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Las Flores - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G173" t="str">
-        <v>2:59</v>
+        <v>2:49</v>
       </c>
       <c r="H173" t="str">
-        <v>Mau y Ricky</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L173" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>To The Moon</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G174" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H174" t="str">
-        <v>Fancy Hagood</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L174" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>MATCHA</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>SABIA</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G175" t="str">
-        <v>2:36</v>
+        <v>7:56</v>
       </c>
       <c r="H175" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>TOMORA</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L175" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>PROWLER</v>
+        <v>Everything U</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PROWLER - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G176" t="str">
-        <v>2:45</v>
+        <v>3:30</v>
       </c>
       <c r="H176" t="str">
-        <v>Waterparks</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L176" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>BLINDFOLD</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:14</v>
+        <v>4:21</v>
       </c>
       <c r="H177" t="str">
-        <v>Wage War</v>
+        <v>ZERB</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L177" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>how far down</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Take My Bones</v>
+        <v>soft pop</v>
       </c>
       <c r="G178" t="str">
-        <v>2:59</v>
+        <v>3:02</v>
       </c>
       <c r="H178" t="str">
-        <v>Camylio</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L178" t="str">
-        <v>how far down - Camylio</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Tell Me Why</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:26</v>
+        <v>3:12</v>
       </c>
       <c r="H179" t="str">
-        <v>Trap Dickey</v>
+        <v>Subtronics</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L179" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Spin</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Spin - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G180" t="str">
-        <v>4:15</v>
+        <v>2:56</v>
       </c>
       <c r="H180" t="str">
-        <v>21 Lil Harold</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L180" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>MILAN</v>
+        <v>Outside</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>MILAN - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:16</v>
+        <v>3:15</v>
       </c>
       <c r="H181" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>Inayah</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L181" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SHABA</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>SHABA - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H182" t="str">
-        <v>SPINALL</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L182" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Forever</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Reflections</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H183" t="str">
-        <v>From Ashes to New</v>
+        <v>Max McNown</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L183" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G184" t="str">
-        <v>2:46</v>
+        <v>4:19</v>
       </c>
       <c r="H184" t="str">
-        <v>Kaleena Zanders</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L184" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Still Suffer</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H185" t="str">
-        <v>Terror</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L185" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Confused</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>For What It's Worth</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H186" t="str">
-        <v>cortex</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L186" t="str">
-        <v>Confused - cortex</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>On The Low</v>
+        <v>Deep Water</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>On The Low - Single</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:29</v>
+        <v>2:33</v>
       </c>
       <c r="H187" t="str">
-        <v>Rene Bonét</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L187" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Wannabe</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Wannabe - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G188" t="str">
-        <v>2:30</v>
+        <v>3:13</v>
       </c>
       <c r="H188" t="str">
-        <v>Corey Kent</v>
+        <v>ERNEST</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L188" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Talking To Jesus</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Middle Child</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:32</v>
+        <v>1:58</v>
       </c>
       <c r="H189" t="str">
-        <v>Amma</v>
+        <v>Marca MP</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L189" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Price of Love</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Into Oblivion</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>3:24</v>
+        <v>3:29</v>
       </c>
       <c r="H190" t="str">
-        <v>Venom</v>
+        <v>Benny G</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L190" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>breakups with best friends</v>
+        <v>Las Flores</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H191" t="str">
-        <v>Zoe Levert</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L191" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Taylor</v>
+        <v>To The Moon</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:15</v>
+        <v>3:42</v>
       </c>
       <c r="H192" t="str">
-        <v>Hayden Everett</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L192" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Yours</v>
+        <v>MATCHA</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Yours - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G193" t="str">
-        <v>4:26</v>
+        <v>2:36</v>
       </c>
       <c r="H193" t="str">
-        <v>Luca Fogale</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L193" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Pepper</v>
+        <v>PROWLER</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Pepper - Single</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:54</v>
+        <v>2:45</v>
       </c>
       <c r="H194" t="str">
-        <v>S.G. Goodman</v>
+        <v>Waterparks</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L194" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>No Driver</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Roses</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>3:48</v>
+        <v>3:14</v>
       </c>
       <c r="H195" t="str">
-        <v>Widowspeak</v>
+        <v>Wage War</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L195" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Catch A Fire</v>
+        <v>how far down</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G196" t="str">
-        <v>3:13</v>
+        <v>2:59</v>
       </c>
       <c r="H196" t="str">
-        <v>Mat Kearney</v>
+        <v>Camylio</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L196" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>GUERILLAZ</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:18</v>
+        <v>2:26</v>
       </c>
       <c r="H197" t="str">
-        <v>H.LLS</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L197" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Powder</v>
+        <v>Spin</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Powder</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:41</v>
+        <v>4:15</v>
       </c>
       <c r="H198" t="str">
-        <v>Nathanial Young</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L198" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Knuckle</v>
+        <v>MILAN</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Knuckle - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:20</v>
+        <v>2:16</v>
       </c>
       <c r="H199" t="str">
-        <v>MexikoDro</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L199" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>For The Ride</v>
+        <v>SHABA</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>For The Ride - Single</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:43</v>
+        <v>2:01</v>
       </c>
       <c r="H200" t="str">
-        <v>Snakehips</v>
+        <v>SPINALL</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L200" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>I Expect Better</v>
+        <v>Forever</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>I Expect Better - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G201" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H201" t="str">
-        <v>daydreamers</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L201" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>WYD</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>WYD - Single</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:36</v>
+        <v>2:46</v>
       </c>
       <c r="H202" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L202" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Strike and Kill</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G203" t="str">
-        <v>4:29</v>
+        <v>2:57</v>
       </c>
       <c r="H203" t="str">
-        <v>DevilDriver</v>
+        <v>Terror</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L203" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
+        <v>Confused</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>For What It's Worth</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:56</v>
+      </c>
+      <c r="H204" t="str">
+        <v>cortex</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Confused - cortex</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>On The Low</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>On The Low - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:29</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Rene Bonét</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+      </c>
+      <c r="L205" t="str">
+        <v>On The Low - Rene Bonét</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Wannabe</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Wannabe - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:30</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Corey Kent</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Wannabe - Corey Kent</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Talking To Jesus</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Middle Child</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:32</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Amma</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Talking To Jesus - Amma</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Kicked Outta Hell</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Kicked Outta Hell - Venom</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>breakups with best friends</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>breakups with best friends - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:22</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Zoe Levert</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+      </c>
+      <c r="L209" t="str">
+        <v>breakups with best friends - Zoe Levert</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Taylor</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>So The Sun Can Pour</v>
+      </c>
+      <c r="G210" t="str">
+        <v>4:15</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Hayden Everett</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Taylor - Hayden Everett</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Yours</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Yours - Single</v>
+      </c>
+      <c r="G211" t="str">
+        <v>4:26</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Luca Fogale</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Yours - Luca Fogale</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Pepper</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Pepper - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>4:54</v>
+      </c>
+      <c r="H212" t="str">
+        <v>S.G. Goodman</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Pepper - S.G. Goodman</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>No Driver</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Roses</v>
+      </c>
+      <c r="G213" t="str">
+        <v>3:48</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Widowspeak</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+      </c>
+      <c r="L213" t="str">
+        <v>No Driver - Widowspeak</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Catch A Fire</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>Catch A Fire - Single</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:13</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Mat Kearney</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Catch A Fire - Mat Kearney</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>GUERILLAZ</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>GUERILLAZ - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>2:18</v>
+      </c>
+      <c r="H215" t="str">
+        <v>H.LLS</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+      </c>
+      <c r="L215" t="str">
+        <v>GUERILLAZ - H.LLS</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Powder</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>Powder</v>
+      </c>
+      <c r="G216" t="str">
+        <v>4:41</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Nathanial Young</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Powder - Nathanial Young</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Knuckle</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v>Knuckle - Single</v>
+      </c>
+      <c r="G217" t="str">
+        <v>2:20</v>
+      </c>
+      <c r="H217" t="str">
+        <v>MexikoDro</v>
+      </c>
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+      </c>
+      <c r="K217" t="str">
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Knuckle - MexikoDro</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>For The Ride</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>For The Ride - Single</v>
+      </c>
+      <c r="G218" t="str">
+        <v>2:43</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Snakehips</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+      </c>
+      <c r="L218" t="str">
+        <v>For The Ride - Snakehips</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>I Expect Better</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v>I Expect Better - Single</v>
+      </c>
+      <c r="G219" t="str">
+        <v>2:19</v>
+      </c>
+      <c r="H219" t="str">
+        <v>daydreamers</v>
+      </c>
+      <c r="I219" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+      </c>
+      <c r="K219" t="str">
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+      </c>
+      <c r="L219" t="str">
+        <v>I Expect Better - daydreamers</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>WYD</v>
+      </c>
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+      </c>
+      <c r="D220" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v>WYD - Single</v>
+      </c>
+      <c r="G220" t="str">
+        <v>2:36</v>
+      </c>
+      <c r="H220" t="str">
+        <v>KARRAHBOOO</v>
+      </c>
+      <c r="I220" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+      </c>
+      <c r="K220" t="str">
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+      </c>
+      <c r="L220" t="str">
+        <v>WYD - KARRAHBOOO</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D221" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G221" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H221" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I221" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J221" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K221" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L221" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
+      <c r="B222" t="str">
+        <v/>
+      </c>
+      <c r="C222" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D204" t="str">
-        <v>2026-04-22</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
+      <c r="D222" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E222" t="str">
+        <v/>
+      </c>
+      <c r="F222" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G204" t="str">
+      <c r="G222" t="str">
         <v>3:32</v>
       </c>
-      <c r="H204" t="str">
+      <c r="H222" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
+      <c r="I222" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J222" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K204" t="str">
+      <c r="K222" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L204" t="str">
+      <c r="L222" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L222"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L222"/>
+  <dimension ref="A1:L206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ימין - מסתובב ברחובות</v>
+        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410584&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://yosmusic.com/%d7%91%d7%95%d7%a6%d7%a8-%d7%a2%d7%a7%d7%99%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%97%d7%99%d7%9d-%d7%9c%d7%a8%d7%92%d7%a2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "אורחים לרגע” של אליעזר בוצר ועקיבא תורג'מן הוא יצירה טעונה מאוד, שנעה בין שבר עמוק לבין מבט מפויס על החיים והנצח. יש בו תחושה כמעט נבואית כאילו הוא מביט על החיים מלמעלה, בפרספקטיבה של זמניות. המשפט החוזר “אנחנו רק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ימין - מסתובב ברחובות</v>
+        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רגב קהלני - כוסות של יין אדום</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410583&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רגב קהלני - כוסות של יין אדום</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קיזל - אמת חיי</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410582&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קיזל - אמת חיי</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מיכאל יגודאייב - הנעליים שנשארו</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410579&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מיכאל יגודאייב - הנעליים שנשארו</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור קקון &amp; שקד סולומון - שבועה באוקטובר</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410578&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Cannons</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור קקון &amp; שקד סולומון - שבועה באוקטובר</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>להקת פיקוד דרום &amp; חני נחמיאס &amp; אביבה אבידן - פרחים בקנה 2026</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410577&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Beck</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>להקת פיקוד דרום &amp; חני נחמיאס &amp; אביבה אבידן - פרחים בקנה 2026</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>טלי רבקה סימן טוב - חזרתי 2026</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410576&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>טלי רבקה סימן טוב - חזרתי 2026</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>זיו אלול - קום לביא</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410575&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>זיו אלול - קום לביא</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אייל אלבז - שיר ליואב</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-04-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410574&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-23</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אייל אלבז - שיר ליואב</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבי אילסון - בזכותם - גרסה ווקאלית</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-04-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410573&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-23</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Beck</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבי אילסון - בזכותם - גרסה ווקאלית</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>האחים בכר - נשאר הגעגוע - גרסה ווקאלית</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-04-22</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410572&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-23</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>האחים בכר - נשאר הגעגוע - גרסה ווקאלית</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אליה לוי - אהבת השם</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-04-22</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410571&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-23</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אליה לוי - אהבת השם</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אליאור מדר - שלוש מילים קטנות</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-04-22</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410570&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-23</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Demi Lovato</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>אליאור מדר - שלוש מילים קטנות</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אבי אילסון &amp; מוטי איידנסון - דיבור של הלב - גרסה ווקאלית</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-04-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410569&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-23</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Madonna</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>אבי אילסון &amp; מוטי איידנסון - דיבור של הלב - גרסה ווקאלית</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-04-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410585&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-23</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Freya Ridings</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>קורין גמליאל - יהיה בסדר קאבר</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-04-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410581&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-23</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>Celine Dion</v>
       </c>
       <c r="I17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>קורין גמליאל - יהיה בסדר קאבר</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-04-22</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410580&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-23</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I18" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Danna</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Cannons</v>
+        <v>ERNEST</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Beck</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Bella White</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Digster Pop Music</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Beck</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>The All-American Rejects</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Armin van Buuren</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Demi Lovato</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Madonna</v>
+        <v>Tyla</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Freya Ridings</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Celine Dion</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Peter Gabriel</v>
+        <v>Loreen</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Jessie Ware</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-23</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>ERNEST</v>
+        <v>Danna</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Dean Lewis</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Bella White</v>
+        <v>James Smith</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Kip Moore</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ava Max</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Ben Gallaher</v>
+        <v>John Summit</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Ava Max</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Johnny Orlando</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Tyla</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Lewis Capaldi</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Lana Del Rey</v>
+        <v>Laufey</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Loreen</v>
+        <v>bleachers</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Tenille Townes</v>
+        <v>LANY</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Danna</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>OneRepublic</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>The Revivalists</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>James Smith</v>
+        <v>florencemachine</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>John Summit</v>
+        <v>HAUSER</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-23</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Danna</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-23</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Conan Gray</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-23</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>TemplesOfficial</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>bleachers</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Nothing But Thieves</v>
+        <v>kenzie</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-23</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>LANY</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-23</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Laufey</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-23</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-23</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-23</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Evanescence</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>florencemachine</v>
+        <v>elijah woods</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Scorpions</v>
+        <v>colby!</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>HAUSER</v>
+        <v>aron!</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Holly Humberstone</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Mae Muller</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Dead Pony</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-23</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Nothing But Thieves</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>kenzie - where do we go</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>kenzie</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Foo Fighters</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Laufey</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Ella Langley</v>
+        <v>We Three</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Mei Semones</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Evanescence</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>elijah woods</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>colby!</v>
+        <v>METTE</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>The Chainsmokers</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>aron!</v>
+        <v>NewDad</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Owen Riegling</v>
+        <v>Danna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>florencemachine</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Teddy Swims</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Kungs</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Sunday (1994)</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-23</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Freya Skye</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Bryan Adams</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B102" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-23</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>We Three</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>earth is turning</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>4:49</v>
       </c>
       <c r="H103" t="str">
-        <v>Dermot Kennedy</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L103" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>drop dead</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>3:44</v>
       </c>
       <c r="H104" t="str">
-        <v>Bebe Rexha</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L104" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>5:03</v>
       </c>
       <c r="H105" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Madonna</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L105" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>First Light</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:24</v>
       </c>
       <c r="H106" t="str">
-        <v>METTE</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L106" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H107" t="str">
-        <v>Saint Harison</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L107" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>2:36</v>
       </c>
       <c r="H108" t="str">
-        <v>NewDad</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L108" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Rackies</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>2:53</v>
       </c>
       <c r="H109" t="str">
-        <v>Danna</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L109" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>3:33</v>
       </c>
       <c r="H110" t="str">
-        <v>florencemachine</v>
+        <v>Tyla</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L110" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Potential</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>4:02</v>
       </c>
       <c r="H111" t="str">
-        <v>HYBE LABELS</v>
+        <v>sombr</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L111" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B112" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>2 weeks ago</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>3:04</v>
       </c>
       <c r="H112" t="str">
-        <v>Kungs</v>
+        <v>Maluma</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L112" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B113" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>2 weeks ago</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>3:32</v>
       </c>
       <c r="H113" t="str">
-        <v>Charlie Puth</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L113" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Better</v>
       </c>
       <c r="B114" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>2 weeks ago</v>
+        <v>U</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:50</v>
       </c>
       <c r="H114" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Baauer</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L114" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B115" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>2 weeks ago</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H115" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Young Miko</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L115" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B116" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>2 weeks ago</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>4:32</v>
       </c>
       <c r="H116" t="str">
-        <v>Madison Cunningham</v>
+        <v>Beck</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L116" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B117" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>2 weeks ago</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>3:14</v>
       </c>
       <c r="H117" t="str">
-        <v>Armin van Buuren</v>
+        <v>DANNA</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L117" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>i just get worse</v>
       </c>
       <c r="B118" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>2 weeks ago</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>3:25</v>
       </c>
       <c r="H118" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L118" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>earth is turning</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G119" t="str">
-        <v>4:49</v>
+        <v>3:23</v>
       </c>
       <c r="H119" t="str">
-        <v>horsegiirL</v>
+        <v>John Summit</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L119" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>drop dead</v>
+        <v>Side Effects</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G120" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H120" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>ZAYN</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L120" t="str">
-        <v>drop dead - Olivia Rodrigo</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>I Feel So Free</v>
+        <v>Numb</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>5:03</v>
+        <v>2:34</v>
       </c>
       <c r="H121" t="str">
-        <v>Madonna</v>
+        <v>JT</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L121" t="str">
-        <v>I Feel So Free - Madonna</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>First Light</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>First Light - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:24</v>
+        <v>3:05</v>
       </c>
       <c r="H122" t="str">
-        <v>Lana Del Rey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L122" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Focu 'Ranni</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H123" t="str">
-        <v>ROSALÍA</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L123" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Middle of Nowhere</v>
+        <v>My Way</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Middle of Nowhere</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:36</v>
+        <v>4:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Riley Green</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L124" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Rackies</v>
+        <v>Ache</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:53</v>
+        <v>4:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Sexyy Red</v>
+        <v>Not-For-Radio</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L125" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>Ache - Not-For-Radio</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G126" t="str">
-        <v>3:33</v>
+        <v>4:09</v>
       </c>
       <c r="H126" t="str">
-        <v>Tyla</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L126" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Potential</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Potential - Single</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:02</v>
+        <v>2:13</v>
       </c>
       <c r="H127" t="str">
-        <v>sombr</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L127" t="str">
-        <v>Potential - sombr</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Pa' la seca</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G128" t="str">
-        <v>3:04</v>
+        <v>3:57</v>
       </c>
       <c r="H128" t="str">
-        <v>Maluma</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L128" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>The Nightlife</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:32</v>
+        <v>4:21</v>
       </c>
       <c r="H129" t="str">
-        <v>Honey Dijon</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L129" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Better</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>U</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:50</v>
+        <v>3:26</v>
       </c>
       <c r="H130" t="str">
-        <v>Baauer</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L130" t="str">
-        <v>Better - Baauer</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>BIAF &lt;3</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:22</v>
       </c>
       <c r="H131" t="str">
-        <v>Young Miko</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L131" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Ride Lonesome</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G132" t="str">
-        <v>4:32</v>
+        <v>2:34</v>
       </c>
       <c r="H132" t="str">
-        <v>Beck</v>
+        <v>MUNA</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L132" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>Superbloom</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>Superbloom</v>
       </c>
       <c r="G133" t="str">
-        <v>3:14</v>
+        <v>4:11</v>
       </c>
       <c r="H133" t="str">
-        <v>DANNA</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L133" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>i just get worse</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>i just get worse - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G134" t="str">
-        <v>3:25</v>
+        <v>1:40</v>
       </c>
       <c r="H134" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L134" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>Make You Move</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:23</v>
+        <v>2:24</v>
       </c>
       <c r="H135" t="str">
-        <v>John Summit</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L135" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Side Effects</v>
+        <v>FERRARI</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>KONNAKOL</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:17</v>
+        <v>2:14</v>
       </c>
       <c r="H136" t="str">
-        <v>ZAYN</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L136" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Numb</v>
+        <v>Por Ella</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Numb - Single</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:34</v>
+        <v>3:01</v>
       </c>
       <c r="H137" t="str">
-        <v>JT</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L137" t="str">
-        <v>Numb - JT</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Stick With You</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G138" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H138" t="str">
-        <v>Labrinth</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L138" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>KGB</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:47</v>
+        <v>2:37</v>
       </c>
       <c r="H139" t="str">
-        <v>Miley Cyrus</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L139" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>My Way</v>
+        <v>Holly!</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>My Way - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G140" t="str">
-        <v>4:02</v>
+        <v>3:10</v>
       </c>
       <c r="H140" t="str">
-        <v>Riley Green</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L140" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Ache</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bloom - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G141" t="str">
-        <v>4:25</v>
+        <v>3:40</v>
       </c>
       <c r="H141" t="str">
-        <v>Not-For-Radio</v>
+        <v>6LACK</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L141" t="str">
-        <v>Ache - Not-For-Radio</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Cut Ties</v>
+        <v>Move Time</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>4:09</v>
+        <v>3:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Anne Hathaway</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L142" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>I Want You</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G143" t="str">
-        <v>2:13</v>
+        <v>3:10</v>
       </c>
       <c r="H143" t="str">
-        <v>Slayyyter</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L143" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Nine Inch Noize</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:57</v>
+        <v>3:11</v>
       </c>
       <c r="H144" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L144" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Boots on the Ground</v>
+        <v>Ring</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:21</v>
+        <v>3:21</v>
       </c>
       <c r="H145" t="str">
-        <v>Massive Attack</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L145" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G146" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H146" t="str">
-        <v>Demi Lovato</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L146" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>I CONDEMN</v>
+        <v>Stay Love</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:22</v>
+        <v>3:26</v>
       </c>
       <c r="H147" t="str">
-        <v>The Kid LAROI</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L147" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wannabeher</v>
+        <v>Love Me</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Dear God</v>
       </c>
       <c r="G148" t="str">
-        <v>2:34</v>
+        <v>4:23</v>
       </c>
       <c r="H148" t="str">
-        <v>MUNA</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L148" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Superbloom</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Superbloom</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:11</v>
+        <v>3:02</v>
       </c>
       <c r="H149" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L149" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Chairwoman Park</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G150" t="str">
-        <v>1:40</v>
+        <v>3:52</v>
       </c>
       <c r="H150" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L150" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Make You Move</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Make You Move - Single</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:24</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Dillon Francis</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L151" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FERRARI</v>
+        <v>Desgraça</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>FERRARI - Single</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G152" t="str">
-        <v>2:14</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Clave Especial</v>
+        <v>Anitta</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L152" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Por Ella</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G153" t="str">
-        <v>3:01</v>
+        <v>2:44</v>
       </c>
       <c r="H153" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L153" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Stick With You</v>
+        <v>Dansons</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H154" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L154" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>KGB</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>KGB - Single</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>2:57</v>
       </c>
       <c r="H155" t="str">
-        <v>ADÉLA</v>
+        <v>Trousdale</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L155" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Holly!</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:10</v>
+        <v>5:21</v>
       </c>
       <c r="H156" t="str">
-        <v>The Band CAMINO</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L156" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Sunday Again</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:40</v>
+        <v>2:49</v>
       </c>
       <c r="H157" t="str">
-        <v>6LACK</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L157" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Move Time</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Move Time - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:32</v>
       </c>
       <c r="H158" t="str">
-        <v>MJ Cole</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L158" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I Want You</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G159" t="str">
-        <v>3:10</v>
+        <v>7:56</v>
       </c>
       <c r="H159" t="str">
-        <v>Cody Johnson</v>
+        <v>TOMORA</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L159" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Straddle Me</v>
+        <v>Everything U</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Straddle Me - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G160" t="str">
-        <v>3:11</v>
+        <v>3:30</v>
       </c>
       <c r="H160" t="str">
-        <v>Mike Clark Jr</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L160" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Ring</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Ring - Single</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:21</v>
+        <v>4:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Queen Naija</v>
+        <v>ZERB</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L161" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Wild</v>
+        <v>soft pop</v>
       </c>
       <c r="G162" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H162" t="str">
-        <v>Ashley McBryde</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L162" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Stay Love</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Survive - EP</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H163" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Subtronics</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L163" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Love Me</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Dear God</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G164" t="str">
-        <v>4:23</v>
+        <v>2:56</v>
       </c>
       <c r="H164" t="str">
-        <v>The Pretty Reckless</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L164" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Outside</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>Dean Lewis</v>
+        <v>Inayah</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L165" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Balboa Park</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Let It Die Here</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:52</v>
+        <v>2:25</v>
       </c>
       <c r="H166" t="str">
-        <v>Linda Perry</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L166" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The One You Loved</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:08</v>
+        <v>3:12</v>
       </c>
       <c r="H167" t="str">
-        <v>Kenya Grace</v>
+        <v>Max McNown</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L167" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Desgraça</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G168" t="str">
-        <v>2:50</v>
+        <v>4:19</v>
       </c>
       <c r="H168" t="str">
-        <v>Anitta</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L168" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:44</v>
+        <v>3:14</v>
       </c>
       <c r="H169" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L169" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Dansons</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Dansons - Single</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G170" t="str">
         <v>3:26</v>
       </c>
       <c r="H170" t="str">
-        <v>Céline Dion</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L170" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Deep Water</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:57</v>
+        <v>2:33</v>
       </c>
       <c r="H171" t="str">
-        <v>Trousdale</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L171" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G172" t="str">
-        <v>5:21</v>
+        <v>3:13</v>
       </c>
       <c r="H172" t="str">
-        <v>This Is Lorelei</v>
+        <v>ERNEST</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L172" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:49</v>
+        <v>1:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Jack Johnson</v>
+        <v>Marca MP</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L173" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Price of Love</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Dream Chaser</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:32</v>
+        <v>3:29</v>
       </c>
       <c r="H174" t="str">
-        <v>Willie Nelson</v>
+        <v>Benny G</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L174" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>Las Flores</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>COME CLOSER</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>7:56</v>
+        <v>2:59</v>
       </c>
       <c r="H175" t="str">
-        <v>TOMORA</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L175" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Everything U</v>
+        <v>To The Moon</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>If This Is It</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:30</v>
+        <v>3:42</v>
       </c>
       <c r="H176" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L176" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>If It's Not Love</v>
+        <v>MATCHA</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G177" t="str">
-        <v>4:21</v>
+        <v>2:36</v>
       </c>
       <c r="H177" t="str">
-        <v>ZERB</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L177" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Our Last Fight</v>
+        <v>PROWLER</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>soft pop</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:02</v>
+        <v>2:45</v>
       </c>
       <c r="H178" t="str">
-        <v>Amy Shark</v>
+        <v>Waterparks</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L178" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G179" t="str">
-        <v>3:12</v>
+        <v>3:14</v>
       </c>
       <c r="H179" t="str">
-        <v>Subtronics</v>
+        <v>Wage War</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L179" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The Perfect One</v>
+        <v>how far down</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G180" t="str">
-        <v>2:56</v>
+        <v>2:59</v>
       </c>
       <c r="H180" t="str">
-        <v>rjtheweirdo</v>
+        <v>Camylio</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L180" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Outside</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Outside - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:15</v>
+        <v>2:26</v>
       </c>
       <c r="H181" t="str">
-        <v>Inayah</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L181" t="str">
-        <v>Outside - Inayah</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Spin</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:25</v>
+        <v>4:15</v>
       </c>
       <c r="H182" t="str">
-        <v>Jessie Reyez</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L182" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>MILAN</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:12</v>
+        <v>2:16</v>
       </c>
       <c r="H183" t="str">
-        <v>Max McNown</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L183" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Heart Stop</v>
+        <v>SHABA</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Get It Honest</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:19</v>
+        <v>2:01</v>
       </c>
       <c r="H184" t="str">
-        <v>The Revivalists</v>
+        <v>SPINALL</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L184" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Don't Ask Me</v>
+        <v>Forever</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G185" t="str">
-        <v>3:14</v>
+        <v>3:38</v>
       </c>
       <c r="H185" t="str">
-        <v>Vincent Mason</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L185" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>OSADÍA</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>OSADÍA - Single</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:26</v>
+        <v>2:46</v>
       </c>
       <c r="H186" t="str">
-        <v>Eden Muñoz</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L186" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Deep Water</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Deep Water - EP</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G187" t="str">
-        <v>2:33</v>
+        <v>2:57</v>
       </c>
       <c r="H187" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Terror</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L187" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Time Is A Thief</v>
+        <v>Confused</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Deep Blue</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G188" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H188" t="str">
-        <v>ERNEST</v>
+        <v>cortex</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L188" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>On The Low</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>1:58</v>
+        <v>3:29</v>
       </c>
       <c r="H189" t="str">
-        <v>Marca MP</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L189" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Price of Love</v>
+        <v>Wannabe</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:29</v>
+        <v>2:30</v>
       </c>
       <c r="H190" t="str">
-        <v>Benny G</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L190" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Las Flores</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Las Flores - Single</v>
+        <v>Middle Child</v>
       </c>
       <c r="G191" t="str">
-        <v>2:59</v>
+        <v>3:32</v>
       </c>
       <c r="H191" t="str">
-        <v>Mau y Ricky</v>
+        <v>Amma</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L191" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>To The Moon</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G192" t="str">
-        <v>3:42</v>
+        <v>3:24</v>
       </c>
       <c r="H192" t="str">
-        <v>Fancy Hagood</v>
+        <v>Venom</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L192" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>MATCHA</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>SABIA</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:36</v>
+        <v>3:22</v>
       </c>
       <c r="H193" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L193" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>PROWLER</v>
+        <v>Taylor</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>PROWLER - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G194" t="str">
-        <v>2:45</v>
+        <v>4:15</v>
       </c>
       <c r="H194" t="str">
-        <v>Waterparks</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L194" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>BLINDFOLD</v>
+        <v>Yours</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:14</v>
+        <v>4:26</v>
       </c>
       <c r="H195" t="str">
-        <v>Wage War</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L195" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>how far down</v>
+        <v>Pepper</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Take My Bones</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:59</v>
+        <v>4:54</v>
       </c>
       <c r="H196" t="str">
-        <v>Camylio</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L196" t="str">
-        <v>how far down - Camylio</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Tell Me Why</v>
+        <v>No Driver</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G197" t="str">
-        <v>2:26</v>
+        <v>3:48</v>
       </c>
       <c r="H197" t="str">
-        <v>Trap Dickey</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L197" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Spin</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Spin - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:15</v>
+        <v>3:13</v>
       </c>
       <c r="H198" t="str">
-        <v>21 Lil Harold</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L198" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>MILAN</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>MILAN - Single</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:16</v>
+        <v>2:18</v>
       </c>
       <c r="H199" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>H.LLS</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L199" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SHABA</v>
+        <v>Powder</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>SHABA - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G200" t="str">
-        <v>2:01</v>
+        <v>4:41</v>
       </c>
       <c r="H200" t="str">
-        <v>SPINALL</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L200" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Forever</v>
+        <v>Knuckle</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Reflections</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:38</v>
+        <v>2:20</v>
       </c>
       <c r="H201" t="str">
-        <v>From Ashes to New</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L201" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>For The Ride</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:46</v>
+        <v>2:43</v>
       </c>
       <c r="H202" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Snakehips</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L202" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-23</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Still Suffer</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:57</v>
+        <v>2:19</v>
       </c>
       <c r="H203" t="str">
-        <v>Terror</v>
+        <v>daydreamers</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L203" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Confused</v>
+        <v>WYD</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-23</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>For What It's Worth</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:56</v>
+        <v>2:36</v>
       </c>
       <c r="H204" t="str">
-        <v>cortex</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L204" t="str">
-        <v>Confused - cortex</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>On The Low</v>
+        <v>Dig Your Own Grave</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-23</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>On The Low - Single</v>
+        <v>Strike and Kill</v>
       </c>
       <c r="G205" t="str">
-        <v>3:29</v>
+        <v>4:29</v>
       </c>
       <c r="H205" t="str">
-        <v>Rene Bonét</v>
+        <v>DevilDriver</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
       </c>
       <c r="L205" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Dig Your Own Grave - DevilDriver</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Wannabe</v>
+        <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-23</v>
@@ -8203,638 +8203,30 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Wannabe - Single</v>
+        <v>The Dead Ones</v>
       </c>
       <c r="G206" t="str">
-        <v>2:30</v>
+        <v>3:32</v>
       </c>
       <c r="H206" t="str">
-        <v>Corey Kent</v>
+        <v>The Last Ten Seconds of Life</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
       <c r="L206" t="str">
-        <v>Wannabe - Corey Kent</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Talking To Jesus</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Middle Child</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:32</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Amma</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Talking To Jesus - Amma</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Kicked Outta Hell</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Into Oblivion</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Venom</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Kicked Outta Hell - Venom</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>breakups with best friends</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>breakups with best friends - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:22</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Zoe Levert</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
-      </c>
-      <c r="L209" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Taylor</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>So The Sun Can Pour</v>
-      </c>
-      <c r="G210" t="str">
-        <v>4:15</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Hayden Everett</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Taylor - Hayden Everett</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Yours</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Yours - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>4:26</v>
-      </c>
-      <c r="H211" t="str">
-        <v>Luca Fogale</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Yours - Luca Fogale</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Pepper</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Pepper - Single</v>
-      </c>
-      <c r="G212" t="str">
-        <v>4:54</v>
-      </c>
-      <c r="H212" t="str">
-        <v>S.G. Goodman</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Pepper - S.G. Goodman</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>No Driver</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Roses</v>
-      </c>
-      <c r="G213" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Widowspeak</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
-      </c>
-      <c r="L213" t="str">
-        <v>No Driver - Widowspeak</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Catch A Fire</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Catch A Fire - Single</v>
-      </c>
-      <c r="G214" t="str">
-        <v>3:13</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Mat Kearney</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
-      </c>
-      <c r="L214" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>GUERILLAZ</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>GUERILLAZ - Single</v>
-      </c>
-      <c r="G215" t="str">
-        <v>2:18</v>
-      </c>
-      <c r="H215" t="str">
-        <v>H.LLS</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
-      </c>
-      <c r="L215" t="str">
-        <v>GUERILLAZ - H.LLS</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Powder</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Powder</v>
-      </c>
-      <c r="G216" t="str">
-        <v>4:41</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Nathanial Young</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
-      </c>
-      <c r="L216" t="str">
-        <v>Powder - Nathanial Young</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Knuckle</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>Knuckle - Single</v>
-      </c>
-      <c r="G217" t="str">
-        <v>2:20</v>
-      </c>
-      <c r="H217" t="str">
-        <v>MexikoDro</v>
-      </c>
-      <c r="I217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
-      </c>
-      <c r="K217" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
-      </c>
-      <c r="L217" t="str">
-        <v>Knuckle - MexikoDro</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>For The Ride</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E218" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v>For The Ride - Single</v>
-      </c>
-      <c r="G218" t="str">
-        <v>2:43</v>
-      </c>
-      <c r="H218" t="str">
-        <v>Snakehips</v>
-      </c>
-      <c r="I218" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J218" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
-      </c>
-      <c r="K218" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
-      </c>
-      <c r="L218" t="str">
-        <v>For The Ride - Snakehips</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>I Expect Better</v>
-      </c>
-      <c r="B219" t="str">
-        <v/>
-      </c>
-      <c r="C219" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
-      </c>
-      <c r="D219" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E219" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v>I Expect Better - Single</v>
-      </c>
-      <c r="G219" t="str">
-        <v>2:19</v>
-      </c>
-      <c r="H219" t="str">
-        <v>daydreamers</v>
-      </c>
-      <c r="I219" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J219" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
-      </c>
-      <c r="K219" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
-      </c>
-      <c r="L219" t="str">
-        <v>I Expect Better - daydreamers</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>WYD</v>
-      </c>
-      <c r="B220" t="str">
-        <v/>
-      </c>
-      <c r="C220" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
-      </c>
-      <c r="D220" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E220" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v>WYD - Single</v>
-      </c>
-      <c r="G220" t="str">
-        <v>2:36</v>
-      </c>
-      <c r="H220" t="str">
-        <v>KARRAHBOOO</v>
-      </c>
-      <c r="I220" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J220" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
-      </c>
-      <c r="K220" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
-      </c>
-      <c r="L220" t="str">
-        <v>WYD - KARRAHBOOO</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Dig Your Own Grave</v>
-      </c>
-      <c r="B221" t="str">
-        <v/>
-      </c>
-      <c r="C221" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
-      </c>
-      <c r="D221" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E221" t="str">
-        <v/>
-      </c>
-      <c r="F221" t="str">
-        <v>Strike and Kill</v>
-      </c>
-      <c r="G221" t="str">
-        <v>4:29</v>
-      </c>
-      <c r="H221" t="str">
-        <v>DevilDriver</v>
-      </c>
-      <c r="I221" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J221" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
-      </c>
-      <c r="K221" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
-      </c>
-      <c r="L221" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>Rat Trap (feat. Nate Johnson)</v>
-      </c>
-      <c r="B222" t="str">
-        <v/>
-      </c>
-      <c r="C222" t="str">
-        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
-      </c>
-      <c r="D222" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E222" t="str">
-        <v/>
-      </c>
-      <c r="F222" t="str">
-        <v>The Dead Ones</v>
-      </c>
-      <c r="G222" t="str">
-        <v>3:32</v>
-      </c>
-      <c r="H222" t="str">
-        <v>The Last Ten Seconds of Life</v>
-      </c>
-      <c r="I222" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J222" t="str">
-        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
-      </c>
-      <c r="K222" t="str">
-        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
-      </c>
-      <c r="L222" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L222"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-23</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%95%d7%a6%d7%a8-%d7%a2%d7%a7%d7%99%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%97%d7%99%d7%9d-%d7%9c%d7%a8%d7%92%d7%a2/</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "אורחים לרגע” של אליעזר בוצר ועקיבא תורג'מן הוא יצירה טעונה מאוד, שנעה בין שבר עמוק לבין מבט מפויס על החיים והנצח. יש בו תחושה כמעט נבואית כאילו הוא מביט על החיים מלמעלה, בפרספקטיבה של זמניות. המשפט החוזר “אנחנו רק</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-23</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-23</v>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-23</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Cannons</v>
+        <v>Beck</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-23</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Beck</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-23</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-23</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-23</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Digster Pop Music</v>
+        <v>Beck</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Beck</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>The All-American Rejects</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-23</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Demi Lovato</v>
+        <v>Madonna</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-23</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Madonna</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-23</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Freya Ridings</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Celine Dion</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-23</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Peter Gabriel</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-23</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-23</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-23</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>The Kid LAROI.</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-23</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>ERNEST</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-23</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-23</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella White</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-23</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Bella White</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-23</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Kip Moore</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-23</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-23</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Ben Gallaher</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-23</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-23</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Johnny Orlando</v>
+        <v>Tyla</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-23</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Tyla</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-23</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-23</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lana Del Rey</v>
+        <v>Loreen</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-23</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Loreen</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Tenille Townes</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Danna</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-23</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Danna</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-23</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>OneRepublic</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>The Revivalists</v>
+        <v>James Smith</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-23</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>James Smith</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-23</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Holly Humberstone</v>
+        <v>Ava Max</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-23</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-23</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-23</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Ava Max</v>
+        <v>Danna</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-23</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Conan Gray</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>TemplesOfficial</v>
+        <v>Laufey</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-23</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Laufey</v>
+        <v>bleachers</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>bleachers</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-23</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>LANY</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>LANY</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-23</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-23</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-23</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Kygo and carter faith</v>
+        <v>florencemachine</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-23</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>florencemachine</v>
+        <v>Scorpions</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Scorpions</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-23</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Holly Humberstone</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Mae Muller</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Dead Pony</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-23</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-23</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jennifer Lopez</v>
+        <v>kenzie</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>kenzie - where do we go</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-23</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>kenzie</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-23</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Foo Fighters</v>
+        <v>Laufey</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Laufey</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-23</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mei Semones</v>
+        <v>Evanescence</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Evanescence</v>
+        <v>elijah woods</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-23</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>elijah woods</v>
+        <v>colby!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-23</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>colby!</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Chainsmokers</v>
+        <v>aron!</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>aron!</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-23</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Owen Riegling</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-23</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-23</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Teddy Swims</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-23</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-23</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Sunday (1994)</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-23</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-23</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Freya Skye</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-23</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Bryan Adams</v>
+        <v>We Three</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-23</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>We Three</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-23</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-23</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Bebe Rexha</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-23</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>The Lemon Twigs</v>
+        <v>METTE</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-23</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>METTE</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-23</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Saint Harison</v>
+        <v>NewDad</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-23</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>NewDad</v>
+        <v>Danna</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-23</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Danna</v>
+        <v>florencemachine</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-23</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>florencemachine</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-23</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>HYBE LABELS</v>
+        <v>Kungs</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-23</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Kungs</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-23</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Charlie Puth</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-23</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Nothing But Thieves</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-23</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Armin van Buuren</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>earth is turning</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>4:49</v>
       </c>
       <c r="H102" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L102" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>earth is turning</v>
+        <v>drop dead</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G103" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H103" t="str">
-        <v>horsegiirL</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L103" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>drop dead</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G104" t="str">
-        <v>3:44</v>
+        <v>5:03</v>
       </c>
       <c r="H104" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Madonna</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L104" t="str">
-        <v>drop dead - Olivia Rodrigo</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Feel So Free</v>
+        <v>First Light</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>CONFESSIONS II</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>5:03</v>
+        <v>3:24</v>
       </c>
       <c r="H105" t="str">
-        <v>Madonna</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L105" t="str">
-        <v>I Feel So Free - Madonna</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>First Light</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>First Light - Single</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G106" t="str">
-        <v>3:24</v>
+        <v>2:50</v>
       </c>
       <c r="H106" t="str">
-        <v>Lana Del Rey</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L106" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Focu 'Ranni</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G107" t="str">
-        <v>2:50</v>
+        <v>2:36</v>
       </c>
       <c r="H107" t="str">
-        <v>ROSALÍA</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L107" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Rackies</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G108" t="str">
-        <v>2:36</v>
+        <v>2:53</v>
       </c>
       <c r="H108" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L108" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Rackies</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H109" t="str">
-        <v>Sexyy Red</v>
+        <v>Tyla</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L109" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>Potential</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:33</v>
+        <v>4:02</v>
       </c>
       <c r="H110" t="str">
-        <v>Tyla</v>
+        <v>sombr</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L110" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Potential</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Potential - Single</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:02</v>
+        <v>3:04</v>
       </c>
       <c r="H111" t="str">
-        <v>sombr</v>
+        <v>Maluma</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L111" t="str">
-        <v>Potential - sombr</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Pa' la seca</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G112" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H112" t="str">
-        <v>Maluma</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L112" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Better</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>The Nightlife</v>
+        <v>U</v>
       </c>
       <c r="G113" t="str">
-        <v>3:32</v>
+        <v>3:50</v>
       </c>
       <c r="H113" t="str">
-        <v>Honey Dijon</v>
+        <v>Baauer</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L113" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Better</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>U</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:50</v>
+        <v>2:50</v>
       </c>
       <c r="H114" t="str">
-        <v>Baauer</v>
+        <v>Young Miko</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L114" t="str">
-        <v>Better - Baauer</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>BIAF &lt;3</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:50</v>
+        <v>4:32</v>
       </c>
       <c r="H115" t="str">
-        <v>Young Miko</v>
+        <v>Beck</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L115" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ride Lonesome</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>4:32</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Beck</v>
+        <v>DANNA</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L116" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>i just get worse</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H117" t="str">
-        <v>DANNA</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L117" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>i just get worse</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>i just get worse - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G118" t="str">
-        <v>3:25</v>
+        <v>3:23</v>
       </c>
       <c r="H118" t="str">
-        <v>Kevian Kraemer</v>
+        <v>John Summit</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L118" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>Side Effects</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G119" t="str">
-        <v>3:23</v>
+        <v>3:17</v>
       </c>
       <c r="H119" t="str">
-        <v>John Summit</v>
+        <v>ZAYN</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L119" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Side Effects</v>
+        <v>Numb</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>KONNAKOL</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H120" t="str">
-        <v>ZAYN</v>
+        <v>JT</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L120" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Numb</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Numb - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:34</v>
+        <v>3:05</v>
       </c>
       <c r="H121" t="str">
-        <v>JT</v>
+        <v>Labrinth</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L121" t="str">
-        <v>Numb - JT</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:05</v>
+        <v>2:47</v>
       </c>
       <c r="H122" t="str">
-        <v>Labrinth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L122" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>My Way</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:47</v>
+        <v>4:02</v>
       </c>
       <c r="H123" t="str">
-        <v>Miley Cyrus</v>
+        <v>Riley Green</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L123" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>My Way</v>
+        <v>Ache</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>My Way - Single</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:02</v>
+        <v>4:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Riley Green</v>
+        <v>Not-For-Radio</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L124" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Ache - Not-For-Radio</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ache</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Bloom - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G125" t="str">
-        <v>4:25</v>
+        <v>4:09</v>
       </c>
       <c r="H125" t="str">
-        <v>Not-For-Radio</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L125" t="str">
-        <v>Ache - Not-For-Radio</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Cut Ties</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:09</v>
+        <v>2:13</v>
       </c>
       <c r="H126" t="str">
-        <v>Anne Hathaway</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L126" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G127" t="str">
-        <v>2:13</v>
+        <v>3:57</v>
       </c>
       <c r="H127" t="str">
-        <v>Slayyyter</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L127" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Nine Inch Noize</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:57</v>
+        <v>4:21</v>
       </c>
       <c r="H128" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L128" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Boots on the Ground</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:21</v>
+        <v>3:26</v>
       </c>
       <c r="H129" t="str">
-        <v>Massive Attack</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L129" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Low Rise Jeans</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:26</v>
+        <v>2:22</v>
       </c>
       <c r="H130" t="str">
-        <v>Demi Lovato</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L130" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>I CONDEMN</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G131" t="str">
-        <v>2:22</v>
+        <v>2:34</v>
       </c>
       <c r="H131" t="str">
-        <v>The Kid LAROI</v>
+        <v>MUNA</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L131" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Wannabeher</v>
+        <v>Superbloom</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Superbloom</v>
       </c>
       <c r="G132" t="str">
-        <v>2:34</v>
+        <v>4:11</v>
       </c>
       <c r="H132" t="str">
-        <v>MUNA</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L132" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Superbloom</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Superbloom</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G133" t="str">
-        <v>4:11</v>
+        <v>1:40</v>
       </c>
       <c r="H133" t="str">
-        <v>Jessie Ware</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L133" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Chairwoman Park</v>
+        <v>Make You Move</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>1:40</v>
+        <v>2:24</v>
       </c>
       <c r="H134" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L134" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Make You Move</v>
+        <v>FERRARI</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Make You Move - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:24</v>
+        <v>2:14</v>
       </c>
       <c r="H135" t="str">
-        <v>Dillon Francis</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L135" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>FERRARI</v>
+        <v>Por Ella</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>FERRARI - Single</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:14</v>
+        <v>3:01</v>
       </c>
       <c r="H136" t="str">
-        <v>Clave Especial</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L136" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Por Ella</v>
+        <v>Stick With You</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G137" t="str">
-        <v>3:01</v>
+        <v>2:33</v>
       </c>
       <c r="H137" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L137" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Stick With You</v>
+        <v>KGB</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:33</v>
+        <v>2:37</v>
       </c>
       <c r="H138" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L138" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>KGB</v>
+        <v>Holly!</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>KGB - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G139" t="str">
-        <v>2:37</v>
+        <v>3:10</v>
       </c>
       <c r="H139" t="str">
-        <v>ADÉLA</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L139" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Holly!</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G140" t="str">
-        <v>3:10</v>
+        <v>3:40</v>
       </c>
       <c r="H140" t="str">
-        <v>The Band CAMINO</v>
+        <v>6LACK</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L140" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Sunday Again</v>
+        <v>Move Time</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:40</v>
+        <v>3:39</v>
       </c>
       <c r="H141" t="str">
-        <v>6LACK</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L141" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Move Time</v>
+        <v>I Want You</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Move Time - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G142" t="str">
-        <v>3:39</v>
+        <v>3:10</v>
       </c>
       <c r="H142" t="str">
-        <v>MJ Cole</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L142" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>I Want You</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:10</v>
+        <v>3:11</v>
       </c>
       <c r="H143" t="str">
-        <v>Cody Johnson</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L143" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Straddle Me</v>
+        <v>Ring</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:11</v>
+        <v>3:21</v>
       </c>
       <c r="H144" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L144" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Ring</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Ring - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G145" t="str">
-        <v>3:21</v>
+        <v>3:24</v>
       </c>
       <c r="H145" t="str">
-        <v>Queen Naija</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L145" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Stay Love</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wild</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>3:24</v>
+        <v>3:26</v>
       </c>
       <c r="H146" t="str">
-        <v>Ashley McBryde</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L146" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Stay Love</v>
+        <v>Love Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Survive - EP</v>
+        <v>Dear God</v>
       </c>
       <c r="G147" t="str">
-        <v>3:26</v>
+        <v>4:23</v>
       </c>
       <c r="H147" t="str">
-        <v>Lewis Capaldi</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L147" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Love Me</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dear God</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:23</v>
+        <v>3:02</v>
       </c>
       <c r="H148" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L148" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G149" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H149" t="str">
-        <v>Dean Lewis</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L149" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Balboa Park</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Let It Die Here</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:52</v>
+        <v>3:08</v>
       </c>
       <c r="H150" t="str">
-        <v>Linda Perry</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L150" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>The One You Loved</v>
+        <v>Desgraça</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>The One You Loved - Single</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>Kenya Grace</v>
+        <v>Anitta</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L151" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Desgraça</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>2:44</v>
       </c>
       <c r="H152" t="str">
-        <v>Anitta</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L152" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Dansons</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:44</v>
+        <v>3:26</v>
       </c>
       <c r="H153" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L153" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Dansons</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Dansons - Single</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:26</v>
+        <v>2:57</v>
       </c>
       <c r="H154" t="str">
-        <v>Céline Dion</v>
+        <v>Trousdale</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L154" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G155" t="str">
-        <v>2:57</v>
+        <v>5:21</v>
       </c>
       <c r="H155" t="str">
-        <v>Trousdale</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L155" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G156" t="str">
-        <v>5:21</v>
+        <v>2:49</v>
       </c>
       <c r="H156" t="str">
-        <v>This Is Lorelei</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L156" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G157" t="str">
-        <v>2:49</v>
+        <v>3:32</v>
       </c>
       <c r="H157" t="str">
-        <v>Jack Johnson</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L157" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Dream Chaser</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G158" t="str">
-        <v>3:32</v>
+        <v>7:56</v>
       </c>
       <c r="H158" t="str">
-        <v>Willie Nelson</v>
+        <v>TOMORA</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L158" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>Everything U</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>COME CLOSER</v>
+        <v>If This Is It</v>
       </c>
       <c r="G159" t="str">
-        <v>7:56</v>
+        <v>3:30</v>
       </c>
       <c r="H159" t="str">
-        <v>TOMORA</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L159" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Everything U</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>If This Is It</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:30</v>
+        <v>4:21</v>
       </c>
       <c r="H160" t="str">
-        <v>DJ Seinfeld</v>
+        <v>ZERB</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L160" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If It's Not Love</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G161" t="str">
-        <v>4:21</v>
+        <v>3:02</v>
       </c>
       <c r="H161" t="str">
-        <v>ZERB</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L161" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Our Last Fight</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>soft pop</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:02</v>
+        <v>3:12</v>
       </c>
       <c r="H162" t="str">
-        <v>Amy Shark</v>
+        <v>Subtronics</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L162" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G163" t="str">
-        <v>3:12</v>
+        <v>2:56</v>
       </c>
       <c r="H163" t="str">
-        <v>Subtronics</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L163" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>The Perfect One</v>
+        <v>Outside</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:56</v>
+        <v>3:15</v>
       </c>
       <c r="H164" t="str">
-        <v>rjtheweirdo</v>
+        <v>Inayah</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L164" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Outside</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Outside - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>2:25</v>
       </c>
       <c r="H165" t="str">
-        <v>Inayah</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L165" t="str">
-        <v>Outside - Inayah</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:25</v>
+        <v>3:12</v>
       </c>
       <c r="H166" t="str">
-        <v>Jessie Reyez</v>
+        <v>Max McNown</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L166" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G167" t="str">
-        <v>3:12</v>
+        <v>4:19</v>
       </c>
       <c r="H167" t="str">
-        <v>Max McNown</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L167" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Heart Stop</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Get It Honest</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:19</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>The Revivalists</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L168" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Don't Ask Me</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:14</v>
+        <v>3:26</v>
       </c>
       <c r="H169" t="str">
-        <v>Vincent Mason</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L169" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>OSADÍA</v>
+        <v>Deep Water</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>3:26</v>
+        <v>2:33</v>
       </c>
       <c r="H170" t="str">
-        <v>Eden Muñoz</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L170" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Deep Water</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Deep Water - EP</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G171" t="str">
-        <v>2:33</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>ERNEST</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L171" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Time Is A Thief</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Deep Blue</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:13</v>
+        <v>1:58</v>
       </c>
       <c r="H172" t="str">
-        <v>ERNEST</v>
+        <v>Marca MP</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L172" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Price of Love</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>1:58</v>
+        <v>3:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Marca MP</v>
+        <v>Benny G</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L173" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Price of Love</v>
+        <v>Las Flores</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H174" t="str">
-        <v>Benny G</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L174" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Las Flores</v>
+        <v>To The Moon</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Las Flores - Single</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H175" t="str">
-        <v>Mau y Ricky</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L175" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>To The Moon</v>
+        <v>MATCHA</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G176" t="str">
-        <v>3:42</v>
+        <v>2:36</v>
       </c>
       <c r="H176" t="str">
-        <v>Fancy Hagood</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L176" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>MATCHA</v>
+        <v>PROWLER</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>SABIA</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:36</v>
+        <v>2:45</v>
       </c>
       <c r="H177" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Waterparks</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L177" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>PROWLER</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>PROWLER - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G178" t="str">
-        <v>2:45</v>
+        <v>3:14</v>
       </c>
       <c r="H178" t="str">
-        <v>Waterparks</v>
+        <v>Wage War</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L178" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>BLINDFOLD</v>
+        <v>how far down</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G179" t="str">
-        <v>3:14</v>
+        <v>2:59</v>
       </c>
       <c r="H179" t="str">
-        <v>Wage War</v>
+        <v>Camylio</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L179" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>how far down</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Take My Bones</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:59</v>
+        <v>2:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Camylio</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L180" t="str">
-        <v>how far down - Camylio</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tell Me Why</v>
+        <v>Spin</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:26</v>
+        <v>4:15</v>
       </c>
       <c r="H181" t="str">
-        <v>Trap Dickey</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L181" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Spin</v>
+        <v>MILAN</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Spin - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:15</v>
+        <v>2:16</v>
       </c>
       <c r="H182" t="str">
-        <v>21 Lil Harold</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L182" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>MILAN</v>
+        <v>SHABA</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>MILAN - Single</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:16</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>SPINALL</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L183" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SHABA</v>
+        <v>Forever</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>SHABA - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>3:38</v>
       </c>
       <c r="H184" t="str">
-        <v>SPINALL</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L184" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Forever</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Reflections</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:38</v>
+        <v>2:46</v>
       </c>
       <c r="H185" t="str">
-        <v>From Ashes to New</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L185" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G186" t="str">
-        <v>2:46</v>
+        <v>2:57</v>
       </c>
       <c r="H186" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Terror</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L186" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>Confused</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Still Suffer</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G187" t="str">
-        <v>2:57</v>
+        <v>2:56</v>
       </c>
       <c r="H187" t="str">
-        <v>Terror</v>
+        <v>cortex</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L187" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Confused</v>
+        <v>On The Low</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>For What It's Worth</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:56</v>
+        <v>3:29</v>
       </c>
       <c r="H188" t="str">
-        <v>cortex</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L188" t="str">
-        <v>Confused - cortex</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>On The Low</v>
+        <v>Wannabe</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>On The Low - Single</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:29</v>
+        <v>2:30</v>
       </c>
       <c r="H189" t="str">
-        <v>Rene Bonét</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L189" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Wannabe</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Wannabe - Single</v>
+        <v>Middle Child</v>
       </c>
       <c r="G190" t="str">
-        <v>2:30</v>
+        <v>3:32</v>
       </c>
       <c r="H190" t="str">
-        <v>Corey Kent</v>
+        <v>Amma</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L190" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Talking To Jesus</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Middle Child</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G191" t="str">
-        <v>3:32</v>
+        <v>3:24</v>
       </c>
       <c r="H191" t="str">
-        <v>Amma</v>
+        <v>Venom</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L191" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Into Oblivion</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H192" t="str">
-        <v>Venom</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L192" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>breakups with best friends</v>
+        <v>Taylor</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G193" t="str">
-        <v>3:22</v>
+        <v>4:15</v>
       </c>
       <c r="H193" t="str">
-        <v>Zoe Levert</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L193" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Taylor</v>
+        <v>Yours</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:15</v>
+        <v>4:26</v>
       </c>
       <c r="H194" t="str">
-        <v>Hayden Everett</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L194" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Yours</v>
+        <v>Pepper</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Yours - Single</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:26</v>
+        <v>4:54</v>
       </c>
       <c r="H195" t="str">
-        <v>Luca Fogale</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L195" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Pepper</v>
+        <v>No Driver</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Pepper - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G196" t="str">
-        <v>4:54</v>
+        <v>3:48</v>
       </c>
       <c r="H196" t="str">
-        <v>S.G. Goodman</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L196" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>No Driver</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Roses</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:48</v>
+        <v>3:13</v>
       </c>
       <c r="H197" t="str">
-        <v>Widowspeak</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L197" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Catch A Fire</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:13</v>
+        <v>2:18</v>
       </c>
       <c r="H198" t="str">
-        <v>Mat Kearney</v>
+        <v>H.LLS</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L198" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>GUERILLAZ</v>
+        <v>Powder</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G199" t="str">
-        <v>2:18</v>
+        <v>4:41</v>
       </c>
       <c r="H199" t="str">
-        <v>H.LLS</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L199" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Powder</v>
+        <v>Knuckle</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Powder</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:41</v>
+        <v>2:20</v>
       </c>
       <c r="H200" t="str">
-        <v>Nathanial Young</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L200" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Knuckle</v>
+        <v>For The Ride</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Knuckle - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:20</v>
+        <v>2:43</v>
       </c>
       <c r="H201" t="str">
-        <v>MexikoDro</v>
+        <v>Snakehips</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L201" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>For The Ride</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>For The Ride - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:43</v>
+        <v>2:19</v>
       </c>
       <c r="H202" t="str">
-        <v>Snakehips</v>
+        <v>daydreamers</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L202" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>I Expect Better</v>
+        <v>WYD</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-23</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>I Expect Better - Single</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:19</v>
+        <v>2:36</v>
       </c>
       <c r="H203" t="str">
-        <v>daydreamers</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L203" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>WYD</v>
+        <v>Dig Your Own Grave</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-23</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>WYD - Single</v>
+        <v>Strike and Kill</v>
       </c>
       <c r="G204" t="str">
-        <v>2:36</v>
+        <v>4:29</v>
       </c>
       <c r="H204" t="str">
-        <v>KARRAHBOOO</v>
+        <v>DevilDriver</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
       </c>
       <c r="L204" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>Dig Your Own Grave - DevilDriver</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-23</v>
@@ -8165,68 +8165,30 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Strike and Kill</v>
+        <v>The Dead Ones</v>
       </c>
       <c r="G205" t="str">
-        <v>4:29</v>
+        <v>3:32</v>
       </c>
       <c r="H205" t="str">
-        <v>DevilDriver</v>
+        <v>The Last Ten Seconds of Life</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
       <c r="L205" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Rat Trap (feat. Nate Johnson)</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>The Dead Ones</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:32</v>
-      </c>
-      <c r="H206" t="str">
-        <v>The Last Ten Seconds of Life</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
-      </c>
-      <c r="L206" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>earth is turning</v>
+        <v>Little More Time</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-23</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G102" t="str">
-        <v>4:49</v>
+        <v>3:38</v>
       </c>
       <c r="H102" t="str">
-        <v>horsegiirL</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L102" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="103">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Better</v>
+        <v>earth is turning</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-23</v>
@@ -4669,25 +4669,25 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>U</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G113" t="str">
-        <v>3:50</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Baauer</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L113" t="str">
-        <v>Better - Baauer</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="114">
@@ -4730,13 +4730,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ride Lonesome</v>
+        <v>Better</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-23</v>
@@ -4745,25 +4745,25 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>U</v>
       </c>
       <c r="G115" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H115" t="str">
-        <v>Beck</v>
+        <v>Baauer</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L115" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="116">
@@ -4806,13 +4806,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>i just get worse</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>i just get worse - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:25</v>
+        <v>4:32</v>
       </c>
       <c r="H117" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Beck</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L117" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>i just get worse</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H118" t="str">
-        <v>John Summit</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L118" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Side Effects</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>KONNAKOL</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G119" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H119" t="str">
-        <v>ZAYN</v>
+        <v>John Summit</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L119" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Numb</v>
+        <v>Side Effects</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Numb - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G120" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H120" t="str">
-        <v>JT</v>
+        <v>ZAYN</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L120" t="str">
-        <v>Numb - JT</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Numb</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H121" t="str">
-        <v>Labrinth</v>
+        <v>JT</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L121" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:47</v>
+        <v>3:05</v>
       </c>
       <c r="H122" t="str">
-        <v>Miley Cyrus</v>
+        <v>Labrinth</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L122" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>My Way</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>My Way - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:02</v>
+        <v>2:47</v>
       </c>
       <c r="H123" t="str">
-        <v>Riley Green</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L123" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Ache</v>
+        <v>My Way</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Bloom - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:25</v>
+        <v>4:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Not-For-Radio</v>
+        <v>Riley Green</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L124" t="str">
-        <v>Ache - Not-For-Radio</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Cut Ties</v>
+        <v>Ache</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:09</v>
+        <v>4:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Anne Hathaway</v>
+        <v>Not-For-Radio</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L125" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Ache - Not-For-Radio</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G126" t="str">
-        <v>2:13</v>
+        <v>4:09</v>
       </c>
       <c r="H126" t="str">
-        <v>Slayyyter</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L126" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Nine Inch Noize</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:57</v>
+        <v>2:13</v>
       </c>
       <c r="H127" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L127" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Boots on the Ground</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G128" t="str">
-        <v>4:21</v>
+        <v>3:57</v>
       </c>
       <c r="H128" t="str">
-        <v>Massive Attack</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L128" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H129" t="str">
-        <v>Demi Lovato</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L129" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>I CONDEMN</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:22</v>
+        <v>3:26</v>
       </c>
       <c r="H130" t="str">
-        <v>The Kid LAROI</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L130" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Wannabeher</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Dancing On The Wall</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H131" t="str">
-        <v>MUNA</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L131" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Superbloom</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Superbloom</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G132" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H132" t="str">
-        <v>Jessie Ware</v>
+        <v>MUNA</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L132" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Chairwoman Park</v>
+        <v>Superbloom</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Superbloom</v>
       </c>
       <c r="G133" t="str">
-        <v>1:40</v>
+        <v>4:11</v>
       </c>
       <c r="H133" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L133" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Make You Move</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Make You Move - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G134" t="str">
-        <v>2:24</v>
+        <v>1:40</v>
       </c>
       <c r="H134" t="str">
-        <v>Dillon Francis</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L134" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>FERRARI</v>
+        <v>Make You Move</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>FERRARI - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:14</v>
+        <v>2:24</v>
       </c>
       <c r="H135" t="str">
-        <v>Clave Especial</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L135" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Por Ella</v>
+        <v>FERRARI</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:01</v>
+        <v>2:14</v>
       </c>
       <c r="H136" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L136" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H137" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L137" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G138" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H138" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L138" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H139" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L139" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H140" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L140" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G141" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H141" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L141" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L142" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G143" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H143" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L143" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:21</v>
+        <v>3:12</v>
       </c>
       <c r="H144" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L144" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H145" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L145" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G146" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H146" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L146" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H147" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L147" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G148" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H148" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L148" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H149" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L149" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G150" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H150" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L150" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L151" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G152" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L152" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G153" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H153" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L153" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H154" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L154" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H155" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L155" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G156" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H156" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L156" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H157" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L157" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G158" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H158" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L158" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G159" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H159" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L159" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G160" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H160" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L160" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L161" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G162" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H162" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L162" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H163" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L163" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G164" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H164" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L164" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L165" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H166" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L166" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H167" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L167" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H168" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L168" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H169" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L169" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H170" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L170" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H171" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L171" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G172" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H172" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L172" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L173" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H174" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L174" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H175" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L175" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H176" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L176" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G177" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H177" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L177" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H178" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L178" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G179" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H179" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L179" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G180" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H180" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L180" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H181" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L181" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H182" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L182" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H183" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L183" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H184" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L184" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G185" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H185" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L185" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H186" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L186" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G187" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H187" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L187" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G188" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H188" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L188" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H189" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L189" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H190" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L190" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G191" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H191" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L191" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G192" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H192" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L192" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H193" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L193" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G194" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H194" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L194" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H195" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L195" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H196" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L196" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G197" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H197" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L197" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H198" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L198" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H199" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L199" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G200" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H200" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L200" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H201" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L201" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H202" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L202" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-23</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H203" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L203" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-23</v>
@@ -8127,68 +8127,106 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H204" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L204" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G205" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H205" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D205" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
+      <c r="D206" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G205" t="str">
+      <c r="G206" t="str">
         <v>3:32</v>
       </c>
-      <c r="H205" t="str">
+      <c r="H206" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K205" t="str">
+      <c r="K206" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L205" t="str">
+      <c r="L206" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>

--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L221"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>חג׳בי - כלה בלבן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410601&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Danna</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>חג׳בי - כלה בלבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410600&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Purple Disco Machine</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410599&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dermot Kennedy</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410598&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Cannons</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>שיראל חדד - יאללה תרקדו</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410597&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Beck</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>שיראל חדד - יאללה תרקדו</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410596&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>פרחי ירושלים - ישראל שלי</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410595&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>פרחי ירושלים - ישראל שלי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>עילאי פרץ - אהבה משולשת</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410594&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Digster Pop Music</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>עילאי פרץ - אהבה משולשת</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>מלכה בי &amp; דותנס - אני יכול</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410593&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-23</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Beck</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>מלכה בי &amp; דותנס - אני יכול</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410592&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-23</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>The All-American Rejects</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410591&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-23</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Armin van Buuren</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>אריאל קנדאבי - מצאתי מקום</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410590&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-23</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Demi Lovato</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>אריאל קנדאבי - מצאתי מקום</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410589&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-23</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Madonna</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>איתיאל - מחרוזת דמעות 2026</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410588&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-23</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Freya Ridings</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>איתיאל - מחרוזת דמעות 2026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>אבנתא דליבא - האור הטוב הזה</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410587&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-23</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Celine Dion</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>אבנתא דליבא - האור הטוב הזה</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Peter Gabriel</v>
+        <v>Danna</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Cannons</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>ERNEST</v>
+        <v>Beck</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dean Lewis</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Bella White</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Kip Moore</v>
+        <v>Beck</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Ben Gallaher</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madonna</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-23</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Tyla</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-23</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lana Del Rey</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Loreen</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Tenille Townes</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>ERNEST</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Danna</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>OneRepublic</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The Revivalists</v>
+        <v>Bella White</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>James Smith</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Holly Humberstone</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Ava Max</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>John Summit</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Ava Max</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Danna</v>
+        <v>Tyla</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Conan Gray</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>TemplesOfficial</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Laufey</v>
+        <v>Loreen</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>bleachers</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>LANY</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Danna</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Kygo and carter faith</v>
+        <v>James Smith</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>florencemachine</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Scorpions</v>
+        <v>Ava Max</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Holly Humberstone</v>
+        <v>John Summit</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>HAUSER</v>
+        <v>Ava Max</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Holly Humberstone</v>
+        <v>Danna</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-23</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Mae Muller</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-23</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Dead Pony</v>
+        <v>Laufey</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-23</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Nothing But Thieves</v>
+        <v>bleachers</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>kenzie - where do we go</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>kenzie</v>
+        <v>LANY</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-23</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Laufey</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B69" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Ella Langley</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Mei Semones</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-23</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Evanescence</v>
+        <v>florencemachine</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B72" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>elijah woods</v>
+        <v>Scorpions</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-23</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>colby!</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B74" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-23</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Chainsmokers</v>
+        <v>HAUSER</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>aron!</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Owen Riegling</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-23</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-23</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Teddy Swims</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B79" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-23</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B80" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-23</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-23</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Sunday (1994)</v>
+        <v>kenzie</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Freya Skye</v>
+        <v>Laufey</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Adams</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>We Three</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Evanescence</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Bebe Rexha</v>
+        <v>elijah woods</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>The Lemon Twigs</v>
+        <v>colby!</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>METTE</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Saint Harison</v>
+        <v>aron!</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>NewDad</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-23</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Danna</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-23</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>florencemachine</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-23</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>HYBE LABELS</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-23</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Kungs</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-23</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Charlie Puth</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-23</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Nothing But Thieves</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-23</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-23</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Madison Cunningham</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Armin van Buuren</v>
+        <v>We Three</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Little More Time</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Dinner Party</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Niall Horan</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>drop dead</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:44</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>drop dead - Olivia Rodrigo</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>I Feel So Free</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>CONFESSIONS II</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>5:03</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>METTE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>I Feel So Free - Madonna</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>First Light</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>First Light - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:24</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Lana Del Rey</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Focu 'Ranni</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>ROSALÍA</v>
+        <v>NewDad</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Middle of Nowhere</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Middle of Nowhere</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Danna</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Rackies</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:53</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Sexyy Red</v>
+        <v>florencemachine</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:33</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Tyla</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Potential</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Potential - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>4:02</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>sombr</v>
+        <v>Kungs</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Potential - sombr</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Pa' la seca</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Maluma</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Nightlife</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>Honey Dijon</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>earth is turning</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>horsegiirL</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BIAF &lt;3</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>Young Miko</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Better</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>U</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>Baauer</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Better - Baauer</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G116" t="str">
-        <v>3:14</v>
+        <v/>
       </c>
       <c r="H116" t="str">
-        <v>DANNA</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ride Lonesome</v>
+        <v>Little More Time</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G117" t="str">
-        <v>4:32</v>
+        <v>3:38</v>
       </c>
       <c r="H117" t="str">
-        <v>Beck</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L117" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>i just get worse</v>
+        <v>drop dead</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>i just get worse - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G118" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H118" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L118" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G119" t="str">
-        <v>3:23</v>
+        <v>5:03</v>
       </c>
       <c r="H119" t="str">
-        <v>John Summit</v>
+        <v>Madonna</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L119" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Side Effects</v>
+        <v>First Light</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>KONNAKOL</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:17</v>
+        <v>3:24</v>
       </c>
       <c r="H120" t="str">
-        <v>ZAYN</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L120" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Numb</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Numb - Single</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G121" t="str">
-        <v>2:34</v>
+        <v>2:50</v>
       </c>
       <c r="H121" t="str">
-        <v>JT</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L121" t="str">
-        <v>Numb - JT</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G122" t="str">
-        <v>3:05</v>
+        <v>2:36</v>
       </c>
       <c r="H122" t="str">
-        <v>Labrinth</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L122" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Rackies</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G123" t="str">
-        <v>2:47</v>
+        <v>2:53</v>
       </c>
       <c r="H123" t="str">
-        <v>Miley Cyrus</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L123" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>My Way</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>My Way - Single</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:02</v>
+        <v>3:33</v>
       </c>
       <c r="H124" t="str">
-        <v>Riley Green</v>
+        <v>Tyla</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L124" t="str">
-        <v>My Way - Riley Green</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ache</v>
+        <v>Potential</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Bloom - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:25</v>
+        <v>4:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Not-For-Radio</v>
+        <v>sombr</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L125" t="str">
-        <v>Ache - Not-For-Radio</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Cut Ties</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H126" t="str">
-        <v>Anne Hathaway</v>
+        <v>Maluma</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L126" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G127" t="str">
-        <v>2:13</v>
+        <v>3:32</v>
       </c>
       <c r="H127" t="str">
-        <v>Slayyyter</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L127" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>earth is turning</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Nine Inch Noize</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G128" t="str">
-        <v>3:57</v>
+        <v>4:49</v>
       </c>
       <c r="H128" t="str">
-        <v>Nine Inch Nails</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L128" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Boots on the Ground</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:21</v>
+        <v>2:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Massive Attack</v>
+        <v>Young Miko</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L129" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Better</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>U</v>
       </c>
       <c r="G130" t="str">
-        <v>3:26</v>
+        <v>3:50</v>
       </c>
       <c r="H130" t="str">
-        <v>Demi Lovato</v>
+        <v>Baauer</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L130" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>I CONDEMN</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:22</v>
+        <v>3:14</v>
       </c>
       <c r="H131" t="str">
-        <v>The Kid LAROI</v>
+        <v>DANNA</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L131" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Wannabeher</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:34</v>
+        <v>4:32</v>
       </c>
       <c r="H132" t="str">
-        <v>MUNA</v>
+        <v>Beck</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L132" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Superbloom</v>
+        <v>i just get worse</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Superbloom</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:11</v>
+        <v>3:25</v>
       </c>
       <c r="H133" t="str">
-        <v>Jessie Ware</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L133" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Chairwoman Park</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G134" t="str">
-        <v>1:40</v>
+        <v>3:23</v>
       </c>
       <c r="H134" t="str">
-        <v>Finneas O’Connell</v>
+        <v>John Summit</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L134" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Make You Move</v>
+        <v>Side Effects</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Make You Move - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G135" t="str">
-        <v>2:24</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Dillon Francis</v>
+        <v>ZAYN</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L135" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>FERRARI</v>
+        <v>Numb</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>FERRARI - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:14</v>
+        <v>2:34</v>
       </c>
       <c r="H136" t="str">
-        <v>Clave Especial</v>
+        <v>JT</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L136" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Por Ella</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:01</v>
+        <v>3:05</v>
       </c>
       <c r="H137" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Labrinth</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L137" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Stick With You</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:33</v>
+        <v>2:47</v>
       </c>
       <c r="H138" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L138" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>KGB</v>
+        <v>My Way</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>KGB - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:37</v>
+        <v>4:02</v>
       </c>
       <c r="H139" t="str">
-        <v>ADÉLA</v>
+        <v>Riley Green</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L139" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Holly!</v>
+        <v>Ache</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:10</v>
+        <v>4:25</v>
       </c>
       <c r="H140" t="str">
-        <v>The Band CAMINO</v>
+        <v>Not For Radio</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L140" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>Ache - Not For Radio</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Sunday Again</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G141" t="str">
-        <v>3:40</v>
+        <v>4:09</v>
       </c>
       <c r="H141" t="str">
-        <v>6LACK</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L141" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Move Time</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Move Time - Single</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:39</v>
+        <v>2:13</v>
       </c>
       <c r="H142" t="str">
-        <v>MJ Cole</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L142" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>I Want You</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G143" t="str">
-        <v>3:10</v>
+        <v>3:57</v>
       </c>
       <c r="H143" t="str">
-        <v>Cody Johnson</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L143" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Straddle Me</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:12</v>
+        <v>4:21</v>
       </c>
       <c r="H144" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L144" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Ring</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Ring - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H145" t="str">
-        <v>Queen Naija</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L145" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Lines In The Carpet</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wild</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:24</v>
+        <v>2:22</v>
       </c>
       <c r="H146" t="str">
-        <v>Ashley McBryde</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L146" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Stay Love</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Survive - EP</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G147" t="str">
-        <v>3:26</v>
+        <v>2:34</v>
       </c>
       <c r="H147" t="str">
-        <v>Lewis Capaldi</v>
+        <v>MUNA</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L147" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Love Me</v>
+        <v>Superbloom</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dear God</v>
+        <v>Superbloom</v>
       </c>
       <c r="G148" t="str">
-        <v>4:23</v>
+        <v>4:11</v>
       </c>
       <c r="H148" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L148" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G149" t="str">
-        <v>3:02</v>
+        <v>1:40</v>
       </c>
       <c r="H149" t="str">
-        <v>Dean Lewis</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L149" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Balboa Park</v>
+        <v>Make You Move</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Let It Die Here</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:52</v>
+        <v>2:24</v>
       </c>
       <c r="H150" t="str">
-        <v>Linda Perry</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L150" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>The One You Loved</v>
+        <v>FERRARI</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>The One You Loved - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>2:14</v>
       </c>
       <c r="H151" t="str">
-        <v>Kenya Grace</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L151" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Desgraça</v>
+        <v>Por Ella</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>Anitta</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L152" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Stick With You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>2:44</v>
+        <v>2:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Stephen Sanchez</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L153" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Dansons</v>
+        <v>KGB</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Dansons - Single</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:26</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Céline Dion</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L154" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Holly!</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G155" t="str">
-        <v>2:57</v>
+        <v>3:10</v>
       </c>
       <c r="H155" t="str">
-        <v>Trousdale</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L155" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G156" t="str">
-        <v>5:21</v>
+        <v>3:40</v>
       </c>
       <c r="H156" t="str">
-        <v>This Is Lorelei</v>
+        <v>6LACK</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L156" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Move Time</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:49</v>
+        <v>3:39</v>
       </c>
       <c r="H157" t="str">
-        <v>Jack Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L157" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>I Want You</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Dream Chaser</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G158" t="str">
-        <v>3:32</v>
+        <v>3:10</v>
       </c>
       <c r="H158" t="str">
-        <v>Willie Nelson</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L158" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>COME CLOSER</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>7:56</v>
+        <v>3:12</v>
       </c>
       <c r="H159" t="str">
-        <v>TOMORA</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L159" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Everything U</v>
+        <v>Ring</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>If This Is It</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:30</v>
+        <v>3:21</v>
       </c>
       <c r="H160" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L160" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If It's Not Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G161" t="str">
-        <v>4:21</v>
+        <v>3:24</v>
       </c>
       <c r="H161" t="str">
-        <v>ZERB</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L161" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Our Last Fight</v>
+        <v>Stay Love</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>soft pop</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G162" t="str">
-        <v>3:02</v>
+        <v>3:26</v>
       </c>
       <c r="H162" t="str">
-        <v>Amy Shark</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L162" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Love Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G163" t="str">
-        <v>3:12</v>
+        <v>4:23</v>
       </c>
       <c r="H163" t="str">
-        <v>Subtronics</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L163" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>The Perfect One</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:56</v>
+        <v>3:02</v>
       </c>
       <c r="H164" t="str">
-        <v>rjtheweirdo</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L164" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Outside</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Outside - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>3:52</v>
       </c>
       <c r="H165" t="str">
-        <v>Inayah</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L165" t="str">
-        <v>Outside - Inayah</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>N.Y.F.F.</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:25</v>
+        <v>3:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Jessie Reyez</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L166" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>Desgraça</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G167" t="str">
-        <v>3:12</v>
+        <v>2:50</v>
       </c>
       <c r="H167" t="str">
-        <v>Max McNown</v>
+        <v>Anitta</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L167" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Heart Stop</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Get It Honest</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G168" t="str">
-        <v>4:19</v>
+        <v>2:44</v>
       </c>
       <c r="H168" t="str">
-        <v>The Revivalists</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L168" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Don't Ask Me</v>
+        <v>Dansons</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:14</v>
+        <v>3:26</v>
       </c>
       <c r="H169" t="str">
-        <v>Vincent Mason</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L169" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>OSADÍA</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:26</v>
+        <v>2:57</v>
       </c>
       <c r="H170" t="str">
-        <v>Eden Muñoz</v>
+        <v>Trousdale</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L170" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Deep Water</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Deep Water - EP</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G171" t="str">
-        <v>2:33</v>
+        <v>5:21</v>
       </c>
       <c r="H171" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L171" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Time Is A Thief</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Deep Blue</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G172" t="str">
-        <v>3:13</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>ERNEST</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L172" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G173" t="str">
-        <v>1:58</v>
+        <v>3:32</v>
       </c>
       <c r="H173" t="str">
-        <v>Marca MP</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L173" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Price of Love</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G174" t="str">
-        <v>3:29</v>
+        <v>7:56</v>
       </c>
       <c r="H174" t="str">
-        <v>Benny G</v>
+        <v>TOMORA</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L174" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Las Flores</v>
+        <v>Everything U</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Las Flores - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G175" t="str">
-        <v>2:59</v>
+        <v>3:30</v>
       </c>
       <c r="H175" t="str">
-        <v>Mau y Ricky</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L175" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>To The Moon</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:42</v>
+        <v>4:21</v>
       </c>
       <c r="H176" t="str">
-        <v>Fancy Hagood</v>
+        <v>ZERB</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L176" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>MATCHA</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>SABIA</v>
+        <v>soft pop</v>
       </c>
       <c r="G177" t="str">
-        <v>2:36</v>
+        <v>3:02</v>
       </c>
       <c r="H177" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L177" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>PROWLER</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>PROWLER - Single</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:45</v>
+        <v>3:12</v>
       </c>
       <c r="H178" t="str">
-        <v>Waterparks</v>
+        <v>Subtronics</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L178" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>BLINDFOLD</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G179" t="str">
-        <v>3:14</v>
+        <v>2:56</v>
       </c>
       <c r="H179" t="str">
-        <v>Wage War</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L179" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>how far down</v>
+        <v>Outside</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Take My Bones</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:59</v>
+        <v>3:15</v>
       </c>
       <c r="H180" t="str">
-        <v>Camylio</v>
+        <v>Inayah</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L180" t="str">
-        <v>how far down - Camylio</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tell Me Why</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H181" t="str">
-        <v>Trap Dickey</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L181" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Spin</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Spin - Single</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:15</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>21 Lil Harold</v>
+        <v>Max McNown</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L182" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>MILAN</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>MILAN - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G183" t="str">
-        <v>2:16</v>
+        <v>4:19</v>
       </c>
       <c r="H183" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L183" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SHABA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>SHABA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>3:14</v>
       </c>
       <c r="H184" t="str">
-        <v>SPINALL</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L184" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Forever</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Reflections</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H185" t="str">
-        <v>From Ashes to New</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L185" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Deep Water</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>2:46</v>
+        <v>2:33</v>
       </c>
       <c r="H186" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L186" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Still Suffer</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G187" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H187" t="str">
-        <v>Terror</v>
+        <v>ERNEST</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L187" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Confused</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>For What It's Worth</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:56</v>
+        <v>1:58</v>
       </c>
       <c r="H188" t="str">
-        <v>cortex</v>
+        <v>Marca MP</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L188" t="str">
-        <v>Confused - cortex</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>On The Low</v>
+        <v>Price of Love</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>On The Low - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G189" t="str">
         <v>3:29</v>
       </c>
       <c r="H189" t="str">
-        <v>Rene Bonét</v>
+        <v>Benny G</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L189" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Wannabe</v>
+        <v>Las Flores</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Wannabe - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:30</v>
+        <v>2:59</v>
       </c>
       <c r="H190" t="str">
-        <v>Corey Kent</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L190" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Talking To Jesus</v>
+        <v>To The Moon</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Middle Child</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:32</v>
+        <v>3:42</v>
       </c>
       <c r="H191" t="str">
-        <v>Amma</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L191" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>MATCHA</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Into Oblivion</v>
+        <v>SABIA</v>
       </c>
       <c r="G192" t="str">
-        <v>3:24</v>
+        <v>2:36</v>
       </c>
       <c r="H192" t="str">
-        <v>Venom</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L192" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>breakups with best friends</v>
+        <v>PROWLER</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:22</v>
+        <v>2:45</v>
       </c>
       <c r="H193" t="str">
-        <v>Zoe Levert</v>
+        <v>Waterparks</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L193" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Taylor</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>4:15</v>
+        <v>3:14</v>
       </c>
       <c r="H194" t="str">
-        <v>Hayden Everett</v>
+        <v>Wage War</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L194" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Yours</v>
+        <v>how far down</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Yours - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G195" t="str">
-        <v>4:26</v>
+        <v>2:59</v>
       </c>
       <c r="H195" t="str">
-        <v>Luca Fogale</v>
+        <v>Camylio</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L195" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Pepper</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Pepper - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>4:54</v>
+        <v>2:26</v>
       </c>
       <c r="H196" t="str">
-        <v>S.G. Goodman</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L196" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>No Driver</v>
+        <v>Spin</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Roses</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:48</v>
+        <v>4:15</v>
       </c>
       <c r="H197" t="str">
-        <v>Widowspeak</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L197" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Catch A Fire</v>
+        <v>MILAN</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H198" t="str">
-        <v>Mat Kearney</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L198" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>GUERILLAZ</v>
+        <v>SHABA</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:18</v>
+        <v>2:01</v>
       </c>
       <c r="H199" t="str">
-        <v>H.LLS</v>
+        <v>SPINALL</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L199" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Powder</v>
+        <v>Forever</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Powder</v>
+        <v>Reflections</v>
       </c>
       <c r="G200" t="str">
-        <v>4:41</v>
+        <v>3:38</v>
       </c>
       <c r="H200" t="str">
-        <v>Nathanial Young</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L200" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Knuckle</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Knuckle - Single</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:20</v>
+        <v>2:46</v>
       </c>
       <c r="H201" t="str">
-        <v>MexikoDro</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L201" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>For The Ride</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>For The Ride - Single</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G202" t="str">
-        <v>2:43</v>
+        <v>2:57</v>
       </c>
       <c r="H202" t="str">
-        <v>Snakehips</v>
+        <v>Terror</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L202" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>I Expect Better</v>
+        <v>Confused</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-23</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G203" t="str">
-        <v>2:19</v>
+        <v>2:56</v>
       </c>
       <c r="H203" t="str">
-        <v>daydreamers</v>
+        <v>cortex</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L203" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>WYD</v>
+        <v>On The Low</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-23</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>WYD - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:36</v>
+        <v>3:29</v>
       </c>
       <c r="H204" t="str">
-        <v>KARRAHBOOO</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L204" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>Wannabe</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-23</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Strike and Kill</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>4:29</v>
+        <v>2:30</v>
       </c>
       <c r="H205" t="str">
-        <v>DevilDriver</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L205" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Rat Trap (feat. Nate Johnson)</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-23</v>
@@ -8203,30 +8203,600 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>The Dead Ones</v>
+        <v>Middle Child</v>
       </c>
       <c r="G206" t="str">
         <v>3:32</v>
       </c>
       <c r="H206" t="str">
+        <v>Amma</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Talking To Jesus - Amma</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Kicked Outta Hell</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Kicked Outta Hell - Venom</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>breakups with best friends</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>breakups with best friends - Single</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:22</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Zoe Levert</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+      </c>
+      <c r="L208" t="str">
+        <v>breakups with best friends - Zoe Levert</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Taylor</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>So The Sun Can Pour</v>
+      </c>
+      <c r="G209" t="str">
+        <v>4:15</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Hayden Everett</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Taylor - Hayden Everett</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Yours</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Yours - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>4:26</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Luca Fogale</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Yours - Luca Fogale</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Pepper</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Pepper - Single</v>
+      </c>
+      <c r="G211" t="str">
+        <v>4:54</v>
+      </c>
+      <c r="H211" t="str">
+        <v>S.G. Goodman</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Pepper - S.G. Goodman</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>No Driver</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Roses</v>
+      </c>
+      <c r="G212" t="str">
+        <v>3:48</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Widowspeak</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+      </c>
+      <c r="L212" t="str">
+        <v>No Driver - Widowspeak</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Catch A Fire</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Catch A Fire - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>3:13</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Mat Kearney</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Catch A Fire - Mat Kearney</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>GUERILLAZ</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>GUERILLAZ - Single</v>
+      </c>
+      <c r="G214" t="str">
+        <v>2:18</v>
+      </c>
+      <c r="H214" t="str">
+        <v>H.LLS</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+      </c>
+      <c r="L214" t="str">
+        <v>GUERILLAZ - H.LLS</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Powder</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Powder</v>
+      </c>
+      <c r="G215" t="str">
+        <v>4:41</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Nathanial Young</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Powder - Nathanial Young</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Knuckle</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>Knuckle - Single</v>
+      </c>
+      <c r="G216" t="str">
+        <v>2:20</v>
+      </c>
+      <c r="H216" t="str">
+        <v>MexikoDro</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Knuckle - MexikoDro</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>For The Ride</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v>For The Ride - Single</v>
+      </c>
+      <c r="G217" t="str">
+        <v>2:43</v>
+      </c>
+      <c r="H217" t="str">
+        <v>Snakehips</v>
+      </c>
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+      </c>
+      <c r="K217" t="str">
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+      </c>
+      <c r="L217" t="str">
+        <v>For The Ride - Snakehips</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>I Expect Better</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>I Expect Better - Single</v>
+      </c>
+      <c r="G218" t="str">
+        <v>2:19</v>
+      </c>
+      <c r="H218" t="str">
+        <v>daydreamers</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+      </c>
+      <c r="L218" t="str">
+        <v>I Expect Better - daydreamers</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>WYD</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v>WYD - Single</v>
+      </c>
+      <c r="G219" t="str">
+        <v>2:36</v>
+      </c>
+      <c r="H219" t="str">
+        <v>KARRAHBOOO</v>
+      </c>
+      <c r="I219" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+      </c>
+      <c r="K219" t="str">
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+      </c>
+      <c r="L219" t="str">
+        <v>WYD - KARRAHBOOO</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D220" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G220" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H220" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I220" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K220" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L220" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Rat Trap (feat. Nate Johnson)</v>
+      </c>
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
+        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
+      </c>
+      <c r="D221" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v>The Dead Ones</v>
+      </c>
+      <c r="G221" t="str">
+        <v>3:32</v>
+      </c>
+      <c r="H221" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
+      <c r="I221" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J221" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K206" t="str">
+      <c r="K221" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L206" t="str">
+      <c r="L221" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L221"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חג׳בי - כלה בלבן קאבר</v>
+        <v>יובל גולד - בית במושב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410601&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410610&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חג׳בי - כלה בלבן קאבר</v>
+        <v>יובל גולד - בית במושב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+        <v>מיטב אמני ישראל - אשת חיל 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410600&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410609&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+        <v>מיטב אמני ישראל - אשת חיל 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+        <v>נאור כהן - לא לבד</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410599&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410608&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+        <v>נאור כהן - לא לבד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
+        <v>מורן לוי - מי אמור</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410598&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410607&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
+        <v>מורן לוי - מי אמור</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שיראל חדד - יאללה תרקדו</v>
+        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410597&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410606&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שיראל חדד - יאללה תרקדו</v>
+        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
+        <v>אהרון כהן - תקופה חרא קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410596&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410605&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -650,7 +650,7 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
+        <v>אהרון כהן - תקופה חרא קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פרחי ירושלים - ישראל שלי</v>
+        <v>אהרון כהן - לב לבן קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410595&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410604&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>פרחי ירושלים - ישראל שלי</v>
+        <v>אהרון כהן - לב לבן קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>עילאי פרץ - אהבה משולשת</v>
+        <v>אהרון כהן - יפה בלבן קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410594&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410603&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,27 +735,27 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>עילאי פרץ - אהבה משולשת</v>
+        <v>אהרון כהן - יפה בלבן קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מלכה בי &amp; דותנס - אני יכול</v>
+        <v>מייקל ג'קסון Songs From The Motion Picture</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410593&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a7%d7%9c-%d7%92%d7%a7%d7%a1%d7%95%d7%9f-songs-from-the-motion-picture/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>האלבום Michael – Songs From The Motion Picture” (2026), שמלווה את הסרט הביוגרפי על מייקל ג'קסון, עומד בפני אתגר מורכב בהרבה מפסקול רגיל: הוא לא רק צריך לשרת סרט, אלא גם לייצג מורשת מוזיקלית מהגדולות בהיסטוריה. לכן הוא נע בין</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מלכה בי &amp; דותנס - אני יכול</v>
+        <v>מייקל ג'קסון Songs From The Motion Picture</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-04-23</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410592&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-04-23</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410591&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,36 +849,36 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אריאל קנדאבי - מצאתי מקום</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-04-23</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410590&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,36 +887,36 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אריאל קנדאבי - מצאתי מקום</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-04-23</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410589&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Cannons</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,36 +925,36 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>איתיאל - מחרוזת דמעות 2026</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-04-23</v>
+        <v>3d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410588&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>3d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Beck</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,36 +963,36 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>איתיאל - מחרוזת דמעות 2026</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אבנתא דליבא - האור הטוב הזה</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-04-23</v>
+        <v>3d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410587&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>3d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>אבנתא דליבא - האור הטוב הזה</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Danna</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Beck</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Cannons</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Beck</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Madonna</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Digster Pop Music</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Beck</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>The All-American Rejects</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Armin van Buuren</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Demi Lovato</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Madonna</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Freya Ridings</v>
+        <v>ERNEST</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Celine Dion</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Peter Gabriel</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bella White</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Jessie Ware</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>ERNEST</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Dean Lewis</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Bella White</v>
+        <v>Tyla</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Kip Moore</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Ben Gallaher</v>
+        <v>Loreen</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Johnny Orlando</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Tyla</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Lana Del Rey</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Loreen</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Bonnie Tyler</v>
+        <v>James Smith</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Tenille Townes</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Ava Max</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Danna</v>
+        <v>John Summit</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>OneRepublic</v>
+        <v>Ava Max</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>The Revivalists</v>
+        <v>Danna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>James Smith</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Holly Humberstone</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>John Summit</v>
+        <v>bleachers</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ava Max</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Danna</v>
+        <v>LANY</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Conan Gray</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>TemplesOfficial</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Laufey</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>bleachers</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Nothing But Thieves</v>
+        <v>florencemachine</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>LANY</v>
+        <v>Scorpions</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>HAUSER</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Kygo and carter faith</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>florencemachine</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Scorpions</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Holly Humberstone</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>HAUSER</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Holly Humberstone</v>
+        <v>kenzie</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Mae Muller</v>
+        <v>Laufey</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Dead Pony</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Evanescence</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>kenzie - where do we go</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>kenzie</v>
+        <v>elijah woods</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Foo Fighters</v>
+        <v>colby!</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Laufey</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Ella Langley</v>
+        <v>aron!</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Mei Semones</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Evanescence</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>elijah woods</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>colby!</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>The Chainsmokers</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>aron!</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Owen Riegling</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Teddy Swims</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>We Three</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Sunday (1994)</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Freya Skye</v>
+        <v>METTE</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Adams</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>We Three</v>
+        <v>NewDad</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Danna</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,33 +4231,33 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Bebe Rexha</v>
+        <v>florencemachine</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,33 +4269,33 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>The Lemon Twigs</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,33 +4307,33 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G104" t="str">
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>METTE</v>
+        <v>Kungs</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,33 +4345,33 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G105" t="str">
         <v/>
       </c>
       <c r="H105" t="str">
-        <v>Saint Harison</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,33 +4383,33 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G106" t="str">
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>NewDad</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,33 +4421,33 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G107" t="str">
         <v/>
       </c>
       <c r="H107" t="str">
-        <v>Danna</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4459,33 +4459,33 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G108" t="str">
         <v/>
       </c>
       <c r="H108" t="str">
-        <v>florencemachine</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4497,33 +4497,33 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G109" t="str">
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>HYBE LABELS</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4535,33 +4535,33 @@
         <v/>
       </c>
       <c r="L109" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G110" t="str">
         <v/>
       </c>
       <c r="H110" t="str">
-        <v>Kungs</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4573,4230 +4573,3584 @@
         <v/>
       </c>
       <c r="L110" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Kehlani</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H111" t="str">
-        <v>Charlie Puth</v>
+        <v>Kehlani</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L111" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Después de ti</v>
       </c>
       <c r="B112" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>2 weeks ago</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>4:35</v>
       </c>
       <c r="H112" t="str">
-        <v>Nothing But Thieves</v>
+        <v>KAROL G</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L112" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B113" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>2 weeks ago</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>3:12</v>
       </c>
       <c r="H113" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L113" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Doors</v>
       </c>
       <c r="B114" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:51</v>
       </c>
       <c r="H114" t="str">
-        <v>Madison Cunningham</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L114" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B115" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>2 weeks ago</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Armin van Buuren</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L115" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B116" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>2 weeks ago</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>2:16</v>
       </c>
       <c r="H116" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L116" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Little More Time</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Dinner Party</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:38</v>
+        <v>2:59</v>
       </c>
       <c r="H117" t="str">
-        <v>Niall Horan</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L117" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>drop dead</v>
+        <v>REDRED</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:44</v>
+        <v>2:43</v>
       </c>
       <c r="H118" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>CORTIS</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L118" t="str">
-        <v>drop dead - Olivia Rodrigo</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I Feel So Free</v>
+        <v>Little More Time</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G119" t="str">
-        <v>5:03</v>
+        <v>3:38</v>
       </c>
       <c r="H119" t="str">
-        <v>Madonna</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L119" t="str">
-        <v>I Feel So Free - Madonna</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>First Light</v>
+        <v>earth is turning</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>First Light - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G120" t="str">
-        <v>3:24</v>
+        <v>4:49</v>
       </c>
       <c r="H120" t="str">
-        <v>Lana Del Rey</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L120" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Focu 'Ranni</v>
+        <v>Better</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>U</v>
       </c>
       <c r="G121" t="str">
-        <v>2:50</v>
+        <v>3:50</v>
       </c>
       <c r="H121" t="str">
-        <v>ROSALÍA</v>
+        <v>Baauer</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L121" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:36</v>
+        <v>4:32</v>
       </c>
       <c r="H122" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Beck</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L122" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rackies</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:53</v>
+        <v>1:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Sexyy Red</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L123" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G124" t="str">
-        <v>3:33</v>
+        <v>2:29</v>
       </c>
       <c r="H124" t="str">
-        <v>Tyla</v>
+        <v>Latto</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L124" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Potential</v>
+        <v>Born To Die</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Potential - Single</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:02</v>
+        <v>2:45</v>
       </c>
       <c r="H125" t="str">
-        <v>sombr</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L125" t="str">
-        <v>Potential - sombr</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pa' la seca</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G126" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H126" t="str">
-        <v>Maluma</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L126" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Nightlife</v>
+        <v>Loveland</v>
       </c>
       <c r="G127" t="str">
-        <v>3:32</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Honey Dijon</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L127" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>earth is turning</v>
+        <v>Fantasy</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G128" t="str">
-        <v>4:49</v>
+        <v>2:21</v>
       </c>
       <c r="H128" t="str">
-        <v>horsegiirL</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L128" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BIAF &lt;3</v>
+        <v>Already Know</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G129" t="str">
-        <v>2:50</v>
+        <v>2:37</v>
       </c>
       <c r="H129" t="str">
-        <v>Young Miko</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L129" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Better</v>
+        <v>PIECES</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>U</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G130" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Baauer</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L130" t="str">
-        <v>Better - Baauer</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>Shimmer</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G131" t="str">
-        <v>3:14</v>
+        <v>2:47</v>
       </c>
       <c r="H131" t="str">
-        <v>DANNA</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L131" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Ride Lonesome</v>
+        <v>Window</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G132" t="str">
-        <v>4:32</v>
+        <v>3:37</v>
       </c>
       <c r="H132" t="str">
-        <v>Beck</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L132" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>i just get worse</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>i just get worse - Single</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:25</v>
+        <v>3:35</v>
       </c>
       <c r="H133" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Korn</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L133" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H134" t="str">
-        <v>John Summit</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L134" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Side Effects</v>
+        <v>La Buena</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>KONNAKOL</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:16</v>
       </c>
       <c r="H135" t="str">
-        <v>ZAYN</v>
+        <v>Carín León</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L135" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Numb</v>
+        <v>You Better Know</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Numb - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G136" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H136" t="str">
-        <v>JT</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L136" t="str">
-        <v>Numb - JT</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:05</v>
+        <v>3:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Labrinth</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L137" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G138" t="str">
-        <v>2:47</v>
+        <v>4:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Miley Cyrus</v>
+        <v>Rostam</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L138" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>My Way</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>My Way - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:02</v>
+        <v>3:19</v>
       </c>
       <c r="H139" t="str">
-        <v>Riley Green</v>
+        <v>mgk</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L139" t="str">
-        <v>My Way - Riley Green</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Ache</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Bloom - Single</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>4:25</v>
+        <v>2:33</v>
       </c>
       <c r="H140" t="str">
-        <v>Not For Radio</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L140" t="str">
-        <v>Ache - Not For Radio</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Cut Ties</v>
+        <v>Door</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G141" t="str">
-        <v>4:09</v>
+        <v>3:54</v>
       </c>
       <c r="H141" t="str">
-        <v>Anne Hathaway</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L141" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:13</v>
+        <v>2:32</v>
       </c>
       <c r="H142" t="str">
-        <v>Slayyyter</v>
+        <v>Ruel</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L142" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Nine Inch Noize</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:57</v>
+        <v>3:17</v>
       </c>
       <c r="H143" t="str">
-        <v>Nine Inch Nails</v>
+        <v>MICO</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L143" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Boots on the Ground</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:21</v>
+        <v>2:52</v>
       </c>
       <c r="H144" t="str">
-        <v>Massive Attack</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L144" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Low Rise Jeans</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H145" t="str">
-        <v>Demi Lovato</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L145" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>I CONDEMN</v>
+        <v>car crash</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:22</v>
+        <v>2:40</v>
       </c>
       <c r="H146" t="str">
-        <v>The Kid LAROI</v>
+        <v>jigitz</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L146" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wannabeher</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Dancing On The Wall</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:34</v>
+        <v>3:22</v>
       </c>
       <c r="H147" t="str">
-        <v>MUNA</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L147" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Superbloom</v>
+        <v>Better Days</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Superbloom</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G148" t="str">
-        <v>4:11</v>
+        <v>3:35</v>
       </c>
       <c r="H148" t="str">
-        <v>Jessie Ware</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L148" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Chairwoman Park</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Location Lost</v>
       </c>
       <c r="G149" t="str">
-        <v>1:40</v>
+        <v>4:32</v>
       </c>
       <c r="H149" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Failure</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L149" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Make You Move</v>
+        <v>Cryogen</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Make You Move - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G150" t="str">
-        <v>2:24</v>
+        <v>5:01</v>
       </c>
       <c r="H150" t="str">
-        <v>Dillon Francis</v>
+        <v>Muse</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L150" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FERRARI</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>FERRARI - Single</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:14</v>
+        <v>1:21</v>
       </c>
       <c r="H151" t="str">
-        <v>Clave Especial</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L151" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Por Ella</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G152" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H152" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L152" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Stick With You</v>
+        <v>HBO</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:33</v>
+        <v>3:42</v>
       </c>
       <c r="H153" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L153" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>KGB</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>KGB - Single</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>3:15</v>
       </c>
       <c r="H154" t="str">
-        <v>ADÉLA</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L154" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Holly!</v>
+        <v>collide</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:10</v>
+        <v>3:43</v>
       </c>
       <c r="H155" t="str">
-        <v>The Band CAMINO</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L155" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Sunday Again</v>
+        <v>freak for you</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:40</v>
+        <v>2:26</v>
       </c>
       <c r="H156" t="str">
-        <v>6LACK</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L156" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Move Time</v>
+        <v>Anymore</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Move Time - Single</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:39</v>
+        <v>2:37</v>
       </c>
       <c r="H157" t="str">
-        <v>MJ Cole</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L157" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>I Want You</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:10</v>
+        <v>3:17</v>
       </c>
       <c r="H158" t="str">
-        <v>Cody Johnson</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L158" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Straddle Me</v>
+        <v>oh child</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Straddle Me - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:12</v>
+        <v>2:02</v>
       </c>
       <c r="H159" t="str">
-        <v>Mike Clark Jr</v>
+        <v>kai devega</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L159" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Ring</v>
+        <v>Dance To This</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Ring - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G160" t="str">
-        <v>3:21</v>
+        <v>2:54</v>
       </c>
       <c r="H160" t="str">
-        <v>Queen Naija</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L160" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Wild</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:24</v>
+        <v>3:58</v>
       </c>
       <c r="H161" t="str">
-        <v>Ashley McBryde</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L161" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Stay Love</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Survive - EP</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:26</v>
+        <v>3:15</v>
       </c>
       <c r="H162" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L162" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Love Me</v>
+        <v>Backwards</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Dear God</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:23</v>
+        <v>3:17</v>
       </c>
       <c r="H163" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L163" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G164" t="str">
-        <v>3:02</v>
+        <v>3:27</v>
       </c>
       <c r="H164" t="str">
-        <v>Dean Lewis</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L164" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Balboa Park</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Let It Die Here</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H165" t="str">
-        <v>Linda Perry</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L165" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>The One You Loved</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The One You Loved - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:08</v>
+        <v>3:42</v>
       </c>
       <c r="H166" t="str">
-        <v>Kenya Grace</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L166" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Desgraça</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:50</v>
+        <v>2:59</v>
       </c>
       <c r="H167" t="str">
-        <v>Anitta</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L167" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Tremolo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G168" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H168" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Metric</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L168" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dansons</v>
+        <v>In the Dark</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dansons - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G169" t="str">
-        <v>3:26</v>
+        <v>3:52</v>
       </c>
       <c r="H169" t="str">
-        <v>Céline Dion</v>
+        <v>Atreyu</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L169" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G170" t="str">
-        <v>2:57</v>
+        <v>4:36</v>
       </c>
       <c r="H170" t="str">
-        <v>Trousdale</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L170" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>5:21</v>
+        <v>3:09</v>
       </c>
       <c r="H171" t="str">
-        <v>This Is Lorelei</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L171" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Grateful</v>
       </c>
       <c r="G172" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H172" t="str">
-        <v>Jack Johnson</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L172" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Full Circle</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Dream Chaser</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Willie Nelson</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L173" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>COME CLOSER</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>7:56</v>
+        <v>3:39</v>
       </c>
       <c r="H174" t="str">
-        <v>TOMORA</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L174" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Everything U</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>If This Is It</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G175" t="str">
-        <v>3:30</v>
+        <v>2:03</v>
       </c>
       <c r="H175" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L175" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>If It's Not Love</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G176" t="str">
-        <v>4:21</v>
+        <v>2:51</v>
       </c>
       <c r="H176" t="str">
-        <v>ZERB</v>
+        <v>Montana 700</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L176" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Our Last Fight</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>soft pop</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:02</v>
+        <v>2:31</v>
       </c>
       <c r="H177" t="str">
-        <v>Amy Shark</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L177" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:12</v>
+        <v>3:28</v>
       </c>
       <c r="H178" t="str">
-        <v>Subtronics</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L178" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The Perfect One</v>
+        <v>Twice</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G179" t="str">
-        <v>2:56</v>
+        <v>2:32</v>
       </c>
       <c r="H179" t="str">
-        <v>rjtheweirdo</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L179" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Outside</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Outside - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:15</v>
+        <v>2:36</v>
       </c>
       <c r="H180" t="str">
-        <v>Inayah</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L180" t="str">
-        <v>Outside - Inayah</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>N.Y.F.F.</v>
+        <v>hide and seek</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:25</v>
+        <v>2:47</v>
       </c>
       <c r="H181" t="str">
-        <v>Jessie Reyez</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L181" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>Be the One</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>3:25</v>
       </c>
       <c r="H182" t="str">
-        <v>Max McNown</v>
+        <v>Adam Port</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L182" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Heart Stop</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Get It Honest</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G183" t="str">
-        <v>4:19</v>
+        <v>4:46</v>
       </c>
       <c r="H183" t="str">
-        <v>The Revivalists</v>
+        <v>Lane 8</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L183" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Don't Ask Me</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:14</v>
+        <v>2:31</v>
       </c>
       <c r="H184" t="str">
-        <v>Vincent Mason</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L184" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>OSADÍA</v>
+        <v>Physical (feat. Kyozo)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/physical-feat-kyozo/1891816798</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Physical (feat. Kyozo) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:26</v>
+        <v>2:40</v>
       </c>
       <c r="H185" t="str">
-        <v>Eden Muñoz</v>
+        <v>J. Worra</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/physical-feat-kyozo/1891816796</v>
       </c>
       <c r="L185" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Physical (feat. Kyozo) - J. Worra</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Deep Water</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Deep Water - EP</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H186" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L186" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Time Is A Thief</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Deep Blue</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:13</v>
+        <v>3:37</v>
       </c>
       <c r="H187" t="str">
-        <v>ERNEST</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L187" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>1:58</v>
+        <v>3:04</v>
       </c>
       <c r="H188" t="str">
-        <v>Marca MP</v>
+        <v>FEYI</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L188" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Price of Love</v>
+        <v>Campeones</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:29</v>
+        <v>3:48</v>
       </c>
       <c r="H189" t="str">
-        <v>Benny G</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L189" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Las Flores</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Las Flores - Single</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G190" t="str">
-        <v>2:59</v>
+        <v>3:27</v>
       </c>
       <c r="H190" t="str">
-        <v>Mau y Ricky</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L190" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>To The Moon</v>
+        <v>tennis practice</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G191" t="str">
-        <v>3:42</v>
+        <v>2:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Fancy Hagood</v>
+        <v>Khatumu</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L191" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>MATCHA</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SABIA</v>
+        <v>Singing</v>
       </c>
       <c r="G192" t="str">
-        <v>2:36</v>
+        <v>3:37</v>
       </c>
       <c r="H192" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L192" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>PROWLER</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>PROWLER - Single</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G193" t="str">
-        <v>2:45</v>
+        <v>3:06</v>
       </c>
       <c r="H193" t="str">
-        <v>Waterparks</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L193" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>BLINDFOLD</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G194" t="str">
-        <v>3:14</v>
+        <v>5:54</v>
       </c>
       <c r="H194" t="str">
-        <v>Wage War</v>
+        <v>Friko</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L194" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>how far down</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Take My Bones</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>2:59</v>
+        <v>7:05</v>
       </c>
       <c r="H195" t="str">
-        <v>Camylio</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L195" t="str">
-        <v>how far down - Camylio</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Tell Me Why</v>
+        <v>Cake</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:26</v>
+        <v>2:36</v>
       </c>
       <c r="H196" t="str">
-        <v>Trap Dickey</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L196" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Spin</v>
+        <v>from a distance</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Spin - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>4:15</v>
+        <v>2:47</v>
       </c>
       <c r="H197" t="str">
-        <v>21 Lil Harold</v>
+        <v>Luz</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L197" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>MILAN</v>
+        <v>Second Hand</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>MILAN - Single</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:16</v>
+        <v>3:24</v>
       </c>
       <c r="H198" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L198" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SHABA</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>SHABA - Single</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G199" t="str">
-        <v>2:01</v>
+        <v>3:08</v>
       </c>
       <c r="H199" t="str">
-        <v>SPINALL</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L199" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Forever</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Reflections</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G200" t="str">
-        <v>3:38</v>
+        <v>2:40</v>
       </c>
       <c r="H200" t="str">
-        <v>From Ashes to New</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L200" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G201" t="str">
-        <v>2:46</v>
+        <v>3:50</v>
       </c>
       <c r="H201" t="str">
-        <v>Kaleena Zanders</v>
+        <v>At The Gates</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L201" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Still Suffer</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G202" t="str">
-        <v>2:57</v>
+        <v>3:35</v>
       </c>
       <c r="H202" t="str">
-        <v>Terror</v>
+        <v>Sepultura</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L202" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Confused</v>
+        <v>Other Hells</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>For What It's Worth</v>
+        <v>Other Hells - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:56</v>
+        <v>2:06</v>
       </c>
       <c r="H203" t="str">
-        <v>cortex</v>
+        <v>Ceremony</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
       </c>
       <c r="L203" t="str">
-        <v>Confused - cortex</v>
+        <v>Other Hells - Ceremony</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>On The Low</v>
+        <v>Hit a Moonshot</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>On The Low - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G204" t="str">
-        <v>3:29</v>
+        <v>4:34</v>
       </c>
       <c r="H204" t="str">
-        <v>Rene Bonét</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
       <c r="L204" t="str">
-        <v>On The Low - Rene Bonét</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Wannabe</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Wannabe - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>2:30</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Corey Kent</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Wannabe - Corey Kent</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Talking To Jesus</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Middle Child</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:32</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Amma</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Talking To Jesus - Amma</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Kicked Outta Hell</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Into Oblivion</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Venom</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Kicked Outta Hell - Venom</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>breakups with best friends</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>breakups with best friends - Single</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:22</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Zoe Levert</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
-      </c>
-      <c r="L208" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Taylor</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>So The Sun Can Pour</v>
-      </c>
-      <c r="G209" t="str">
-        <v>4:15</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Hayden Everett</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Taylor - Hayden Everett</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Yours</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Yours - Single</v>
-      </c>
-      <c r="G210" t="str">
-        <v>4:26</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Luca Fogale</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Yours - Luca Fogale</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Pepper</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Pepper - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>4:54</v>
-      </c>
-      <c r="H211" t="str">
-        <v>S.G. Goodman</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Pepper - S.G. Goodman</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>No Driver</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Roses</v>
-      </c>
-      <c r="G212" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Widowspeak</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
-      </c>
-      <c r="L212" t="str">
-        <v>No Driver - Widowspeak</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Catch A Fire</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Catch A Fire - Single</v>
-      </c>
-      <c r="G213" t="str">
-        <v>3:13</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Mat Kearney</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
-      </c>
-      <c r="L213" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>GUERILLAZ</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>GUERILLAZ - Single</v>
-      </c>
-      <c r="G214" t="str">
-        <v>2:18</v>
-      </c>
-      <c r="H214" t="str">
-        <v>H.LLS</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
-      </c>
-      <c r="L214" t="str">
-        <v>GUERILLAZ - H.LLS</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Powder</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Powder</v>
-      </c>
-      <c r="G215" t="str">
-        <v>4:41</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Nathanial Young</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Powder - Nathanial Young</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Knuckle</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Knuckle - Single</v>
-      </c>
-      <c r="G216" t="str">
-        <v>2:20</v>
-      </c>
-      <c r="H216" t="str">
-        <v>MexikoDro</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
-      </c>
-      <c r="L216" t="str">
-        <v>Knuckle - MexikoDro</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>For The Ride</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>For The Ride - Single</v>
-      </c>
-      <c r="G217" t="str">
-        <v>2:43</v>
-      </c>
-      <c r="H217" t="str">
-        <v>Snakehips</v>
-      </c>
-      <c r="I217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
-      </c>
-      <c r="K217" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
-      </c>
-      <c r="L217" t="str">
-        <v>For The Ride - Snakehips</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>I Expect Better</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E218" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v>I Expect Better - Single</v>
-      </c>
-      <c r="G218" t="str">
-        <v>2:19</v>
-      </c>
-      <c r="H218" t="str">
-        <v>daydreamers</v>
-      </c>
-      <c r="I218" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J218" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
-      </c>
-      <c r="K218" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
-      </c>
-      <c r="L218" t="str">
-        <v>I Expect Better - daydreamers</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>WYD</v>
-      </c>
-      <c r="B219" t="str">
-        <v/>
-      </c>
-      <c r="C219" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
-      </c>
-      <c r="D219" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E219" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v>WYD - Single</v>
-      </c>
-      <c r="G219" t="str">
-        <v>2:36</v>
-      </c>
-      <c r="H219" t="str">
-        <v>KARRAHBOOO</v>
-      </c>
-      <c r="I219" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J219" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
-      </c>
-      <c r="K219" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
-      </c>
-      <c r="L219" t="str">
-        <v>WYD - KARRAHBOOO</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Dig Your Own Grave</v>
-      </c>
-      <c r="B220" t="str">
-        <v/>
-      </c>
-      <c r="C220" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
-      </c>
-      <c r="D220" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E220" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v>Strike and Kill</v>
-      </c>
-      <c r="G220" t="str">
-        <v>4:29</v>
-      </c>
-      <c r="H220" t="str">
-        <v>DevilDriver</v>
-      </c>
-      <c r="I220" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J220" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
-      </c>
-      <c r="K220" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
-      </c>
-      <c r="L220" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Rat Trap (feat. Nate Johnson)</v>
-      </c>
-      <c r="B221" t="str">
-        <v/>
-      </c>
-      <c r="C221" t="str">
-        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
-      </c>
-      <c r="D221" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E221" t="str">
-        <v/>
-      </c>
-      <c r="F221" t="str">
-        <v>The Dead Ones</v>
-      </c>
-      <c r="G221" t="str">
-        <v>3:32</v>
-      </c>
-      <c r="H221" t="str">
-        <v>The Last Ten Seconds of Life</v>
-      </c>
-      <c r="I221" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J221" t="str">
-        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
-      </c>
-      <c r="K221" t="str">
-        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
-      </c>
-      <c r="L221" t="str">
-        <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
+        <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L221"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד - בית במושב</v>
+        <v>יובל גולד – בית במושב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410610&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%91%d7%99%d7%aa-%d7%91%d7%9e%d7%95%d7%a9%d7%91/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הטקסט של „"בית במושב” של יובל גולד עובד בדיוק על הקו שבין פשטות יומיומית לבין הצהרה רגשית עמוקה, בקצב שמשרת נרטיב אישי בבלדת רוק נוגה. השיר נשען על קצב יציב (כמעט “הליכה” רגועה), בלי שינויים דרמטיים: בינוני-איטי שיוצר תחושת אינטימיות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד - בית במושב</v>
+        <v>יובל גולד – בית במושב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיטב אמני ישראל - אשת חיל 2026</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-24</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410609&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-24</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיטב אמני ישראל - אשת חיל 2026</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נאור כהן - לא לבד</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-24</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410608&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-24</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נאור כהן - לא לבד</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מורן לוי - מי אמור</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-24</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410607&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-24</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מורן לוי - מי אמור</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-24</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410606&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-24</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Cannons</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אהרון כהן - תקופה חרא קאבר</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-24</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410605&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-24</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Beck</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אהרון כהן - תקופה חרא קאבר</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אהרון כהן - לב לבן קאבר</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-24</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410604&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-24</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אהרון כהן - לב לבן קאבר</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אהרון כהן - יפה בלבן קאבר</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-24</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410603&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-24</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אהרון כהן - יפה בלבן קאבר</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-04-24</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a7%d7%9c-%d7%92%d7%a7%d7%a1%d7%95%d7%9f-songs-from-the-motion-picture/</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-24</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>האלבום Michael – Songs From The Motion Picture” (2026), שמלווה את הסרט הביוגרפי על מייקל ג'קסון, עומד בפני אתגר מורכב בהרבה מפסקול רגיל: הוא לא רק צריך לשרת סרט, אלא גם לייצג מורשת מוזיקלית מהגדולות בהיסטוריה. לכן הוא נע בין</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I10" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B11" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-24</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Danna</v>
+        <v>Beck</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-24</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Purple Disco Machine</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B13" t="str">
-        <v>2d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-24</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-24</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Cannons</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-24</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Beck</v>
+        <v>Madonna</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-24</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B17" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-24</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B18" t="str">
-        <v>3d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-24</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Digster Pop Music</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B19" t="str">
-        <v>3d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-24</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Beck</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B20" t="str">
-        <v>4d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-24</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>The All-American Rejects</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-24</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-24</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Demi Lovato</v>
+        <v>ERNEST</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B23" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-24</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Madonna</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-24</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Freya Ridings</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-24</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Celine Dion</v>
+        <v>Bella White</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B26" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-24</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Peter Gabriel</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-24</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-24</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jessie Ware</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-24</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-24</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>ERNEST</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-24</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Tyla</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-24</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Dean Lewis</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-24</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Bella White</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-24</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Kip Moore</v>
+        <v>Loreen</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-24</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-24</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Ben Gallaher</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-24</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B38" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-24</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Johnny Orlando</v>
+        <v>Danna</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-24</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Tyla</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-24</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lewis Capaldi</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B41" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-24</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Lana Del Rey</v>
+        <v>James Smith</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B42" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-24</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Loreen</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-24</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Ava Max</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B44" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-24</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Tenille Townes</v>
+        <v>John Summit</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-24</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Ava Max</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-24</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-24</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>OneRepublic</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-24</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>The Revivalists</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-24</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>James Smith</v>
+        <v>Laufey</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-24</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Holly Humberstone</v>
+        <v>bleachers</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-24</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Ava Max</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-24</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>John Summit</v>
+        <v>LANY</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>9d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-24</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Ava Max</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>9d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-24</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Danna</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>9d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-24</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Conan Gray</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-24</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>TemplesOfficial</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>10d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-24</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Laufey</v>
+        <v>florencemachine</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B58" t="str">
-        <v>10d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-24</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>bleachers</v>
+        <v>Scorpions</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>11d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-24</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B60" t="str">
-        <v>11d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-24</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>LANY</v>
+        <v>HAUSER</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-24</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-24</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-24</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-24</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B65" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-24</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>florencemachine</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B66" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-24</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Scorpions</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B67" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-24</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Holly Humberstone</v>
+        <v>kenzie</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-24</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>HAUSER</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B69" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-24</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Holly Humberstone</v>
+        <v>Laufey</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-24</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-24</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mae Muller</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-24</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Dead Pony</v>
+        <v>Evanescence</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-24</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Nothing But Thieves</v>
+        <v>elijah woods</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-24</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Jennifer Lopez</v>
+        <v>colby!</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kenzie - where do we go</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-24</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>kenzie</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-24</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Foo Fighters</v>
+        <v>aron!</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-24</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Laufey</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-24</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Ella Langley</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-24</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Mei Semones</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-24</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Evanescence</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-24</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>elijah woods</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-24</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>colby!</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-24</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>The Chainsmokers</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-24</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>aron!</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-24</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Owen Riegling</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-24</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>We Three</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-24</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Teddy Swims</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-24</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-24</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-24</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Sunday (1994)</v>
+        <v>METTE</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-24</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-24</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Freya Skye</v>
+        <v>NewDad</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-24</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Bryan Adams</v>
+        <v>Danna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-24</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>We Three</v>
+        <v>florencemachine</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-24</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Dermot Kennedy</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-24</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Bebe Rexha</v>
+        <v>Kungs</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-24</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-24</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>METTE</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-24</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Saint Harison</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-24</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>NewDad</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-24</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Danna</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-24</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>florencemachine</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B103" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-24</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2w ago</v>
+        <v>Kehlani</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H103" t="str">
-        <v>HYBE LABELS</v>
+        <v>Kehlani</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L103" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Después de ti</v>
       </c>
       <c r="B104" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-24</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2w ago</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>4:35</v>
       </c>
       <c r="H104" t="str">
-        <v>Kungs</v>
+        <v>KAROL G</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L104" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B105" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-24</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2w ago</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:12</v>
       </c>
       <c r="H105" t="str">
-        <v>Charlie Puth</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L105" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Doors</v>
       </c>
       <c r="B106" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-24</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2w ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B107" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-24</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2w ago</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H107" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L107" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B108" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-24</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2w ago</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>2:16</v>
       </c>
       <c r="H108" t="str">
-        <v>Madison Cunningham</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L108" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B109" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-24</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2w ago</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H109" t="str">
-        <v>Armin van Buuren</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L109" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>REDRED</v>
       </c>
       <c r="B110" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-24</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2w ago</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>CORTIS</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L110" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>Little More Time</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-24</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Kehlani</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G111" t="str">
-        <v>3:06</v>
+        <v>3:38</v>
       </c>
       <c r="H111" t="str">
-        <v>Kehlani</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L111" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Después de ti</v>
+        <v>earth is turning</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-24</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Después de ti - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G112" t="str">
-        <v>4:35</v>
+        <v>4:49</v>
       </c>
       <c r="H112" t="str">
-        <v>KAROL G</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L112" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dando Vueltas</v>
+        <v>Better</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-24</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>U</v>
       </c>
       <c r="G113" t="str">
-        <v>3:12</v>
+        <v>3:50</v>
       </c>
       <c r="H113" t="str">
-        <v>Rauw Alejandro</v>
+        <v>Baauer</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L113" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Doors</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-24</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Great Divide</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:51</v>
+        <v>4:32</v>
       </c>
       <c r="H114" t="str">
-        <v>Noah Kahan</v>
+        <v>Beck</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L114" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-24</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:48</v>
+        <v>1:56</v>
       </c>
       <c r="H115" t="str">
-        <v>Ella Langley</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L115" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Todos nos Shipean</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-24</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G116" t="str">
-        <v>2:16</v>
+        <v>2:29</v>
       </c>
       <c r="H116" t="str">
-        <v>Fuerza Regida</v>
+        <v>Latto</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L116" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ojitos Bellos</v>
+        <v>Born To Die</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-24</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:59</v>
+        <v>2:45</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L117" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>REDRED</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-24</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Florescence</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>CORTIS</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L118" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Little More Time</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-24</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dinner Party</v>
+        <v>Loveland</v>
       </c>
       <c r="G119" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Niall Horan</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L119" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>earth is turning</v>
+        <v>Fantasy</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-24</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G120" t="str">
-        <v>4:49</v>
+        <v>2:21</v>
       </c>
       <c r="H120" t="str">
-        <v>horsegiirL</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L120" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Better</v>
+        <v>Already Know</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-24</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>U</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G121" t="str">
-        <v>3:50</v>
+        <v>2:37</v>
       </c>
       <c r="H121" t="str">
-        <v>Baauer</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L121" t="str">
-        <v>Better - Baauer</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Ride Lonesome</v>
+        <v>PIECES</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-24</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G122" t="str">
-        <v>4:32</v>
+        <v>3:25</v>
       </c>
       <c r="H122" t="str">
-        <v>Beck</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L122" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Shimmer</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-24</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G123" t="str">
-        <v>1:56</v>
+        <v>2:47</v>
       </c>
       <c r="H123" t="str">
-        <v>Billie Eilish</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L123" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>Window</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-24</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Big Mama</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G124" t="str">
-        <v>2:29</v>
+        <v>3:37</v>
       </c>
       <c r="H124" t="str">
-        <v>Latto</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L124" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Born To Die</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-24</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Born To Die - Single</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:45</v>
+        <v>3:35</v>
       </c>
       <c r="H125" t="str">
-        <v>Shaboozey</v>
+        <v>Korn</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L125" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-24</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Florescence</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G126" t="str">
-        <v>3:08</v>
+        <v>2:52</v>
       </c>
       <c r="H126" t="str">
-        <v>Maisie Peters</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L126" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Tiny Raisin</v>
+        <v>La Buena</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-24</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Loveland</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:16</v>
       </c>
       <c r="H127" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Carín León</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L127" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Fantasy</v>
+        <v>You Better Know</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-24</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G128" t="str">
-        <v>2:21</v>
+        <v>3:13</v>
       </c>
       <c r="H128" t="str">
-        <v>Demi Lovato</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L128" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Already Know</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-24</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:37</v>
+        <v>3:35</v>
       </c>
       <c r="H129" t="str">
-        <v>The Chainsmokers</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L129" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>PIECES</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-24</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>American Stories</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>4:00</v>
       </c>
       <c r="H130" t="str">
-        <v>The Kid LAROI</v>
+        <v>Rostam</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L130" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Shimmer</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-24</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Toy With Me</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:47</v>
+        <v>3:19</v>
       </c>
       <c r="H131" t="str">
-        <v>Meghan Trainor</v>
+        <v>mgk</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L131" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Window</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-24</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Your Favorite Toy</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:37</v>
+        <v>2:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Foo Fighters</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L132" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Reward the Scars</v>
+        <v>Door</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-24</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G133" t="str">
-        <v>3:35</v>
+        <v>3:54</v>
       </c>
       <c r="H133" t="str">
-        <v>Korn</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L133" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Songs About Us</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-24</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Songs About Us</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:52</v>
+        <v>2:32</v>
       </c>
       <c r="H134" t="str">
-        <v>Jason Aldean</v>
+        <v>Ruel</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L134" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>La Buena</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-24</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>La Buena - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:16</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Carín León</v>
+        <v>MICO</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L135" t="str">
-        <v>La Buena - Carín León</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>You Better Know</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-24</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:13</v>
+        <v>2:52</v>
       </c>
       <c r="H136" t="str">
-        <v>Ebony Riley</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L136" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Planting Tomatoes</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-24</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:35</v>
+        <v>3:23</v>
       </c>
       <c r="H137" t="str">
-        <v>Lucy Dacus</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L137" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Back of a Truck</v>
+        <v>car crash</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-24</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>American Stories</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>4:00</v>
+        <v>2:40</v>
       </c>
       <c r="H138" t="str">
-        <v>Rostam</v>
+        <v>jigitz</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L138" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>FIX UR FACE</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-24</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:19</v>
+        <v>3:22</v>
       </c>
       <c r="H139" t="str">
-        <v>mgk</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L139" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>CELEBRATION</v>
+        <v>Better Days</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-24</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:33</v>
+        <v>3:35</v>
       </c>
       <c r="H140" t="str">
-        <v>LE SSERAFIM</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L140" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Door</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-24</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>Location Lost</v>
       </c>
       <c r="G141" t="str">
-        <v>3:54</v>
+        <v>4:32</v>
       </c>
       <c r="H141" t="str">
-        <v>Conan Gray</v>
+        <v>Failure</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L141" t="str">
-        <v>Door - Conan Gray</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Hate Myself</v>
+        <v>Cryogen</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-24</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Hate Myself - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G142" t="str">
-        <v>2:32</v>
+        <v>5:01</v>
       </c>
       <c r="H142" t="str">
-        <v>Ruel</v>
+        <v>Muse</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L142" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DREAMBOY</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-24</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G143" t="str">
-        <v>3:17</v>
+        <v>1:21</v>
       </c>
       <c r="H143" t="str">
-        <v>MICO</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L143" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-24</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G144" t="str">
-        <v>2:52</v>
+        <v>3:39</v>
       </c>
       <c r="H144" t="str">
-        <v>Daniel Seavey</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L144" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>HBO</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-24</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:23</v>
+        <v>3:42</v>
       </c>
       <c r="H145" t="str">
-        <v>The Two Lips</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L145" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>car crash</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-24</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>car crash - Single</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:40</v>
+        <v>3:15</v>
       </c>
       <c r="H146" t="str">
-        <v>jigitz</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L146" t="str">
-        <v>car crash - jigitz</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>All This Disaster</v>
+        <v>collide</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-24</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>All This Disaster - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G147" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H147" t="str">
-        <v>Sarah McLachlan</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L147" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Better Days</v>
+        <v>freak for you</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-24</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:35</v>
+        <v>2:26</v>
       </c>
       <c r="H148" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L148" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The Rising Skyline</v>
+        <v>Anymore</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-24</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Location Lost</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:32</v>
+        <v>2:37</v>
       </c>
       <c r="H149" t="str">
-        <v>Failure</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L149" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cryogen</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-24</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>The Wow! Signal</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G150" t="str">
-        <v>5:01</v>
+        <v>3:17</v>
       </c>
       <c r="H150" t="str">
-        <v>Muse</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L150" t="str">
-        <v>Cryogen - Muse</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Harry Hole Theme</v>
+        <v>oh child</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-24</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>1:21</v>
+        <v>2:02</v>
       </c>
       <c r="H151" t="str">
-        <v>Nick Cave</v>
+        <v>kai devega</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L151" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Dance To This</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-24</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Ritual</v>
       </c>
       <c r="G152" t="str">
-        <v>3:39</v>
+        <v>2:54</v>
       </c>
       <c r="H152" t="str">
-        <v>Genesis Owusu</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L152" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>HBO</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-24</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>HBO - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:42</v>
+        <v>3:58</v>
       </c>
       <c r="H153" t="str">
-        <v>Yung Gravy</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L153" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Need For Speed</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-24</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Need For Speed - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G154" t="str">
         <v>3:15</v>
       </c>
       <c r="H154" t="str">
-        <v>Kim Petras</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L154" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>collide</v>
+        <v>Backwards</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-24</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H155" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L155" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>freak for you</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-24</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>freak for you - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G156" t="str">
-        <v>2:26</v>
+        <v>3:27</v>
       </c>
       <c r="H156" t="str">
-        <v>Haiden Henderson</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L156" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Anymore</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-24</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:37</v>
+        <v>3:43</v>
       </c>
       <c r="H157" t="str">
-        <v>Asha Banks</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L157" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Why Am I Here</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-24</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:17</v>
+        <v>3:42</v>
       </c>
       <c r="H158" t="str">
-        <v>Presley Regier</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L158" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>oh child</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-24</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>oh child - Single</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:02</v>
+        <v>2:59</v>
       </c>
       <c r="H159" t="str">
-        <v>kai devega</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L159" t="str">
-        <v>oh child - kai devega</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Dance To This</v>
+        <v>Tremolo</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-24</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Ritual</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G160" t="str">
-        <v>2:54</v>
+        <v>3:43</v>
       </c>
       <c r="H160" t="str">
-        <v>Icona Pop</v>
+        <v>Metric</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L160" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>In the Dark</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-24</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G161" t="str">
-        <v>3:58</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Tauren Wells</v>
+        <v>Atreyu</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L161" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>You Can Have Him</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-24</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G162" t="str">
-        <v>3:15</v>
+        <v>4:36</v>
       </c>
       <c r="H162" t="str">
-        <v>Carly Pearce</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L162" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Backwards</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-24</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Backwards - Single</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:17</v>
+        <v>3:09</v>
       </c>
       <c r="H163" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L163" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-24</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Serial Romantic</v>
+        <v>Grateful</v>
       </c>
       <c r="G164" t="str">
-        <v>3:27</v>
+        <v>4:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Jai'Len Josey</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L164" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Full Circle</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-24</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>Isaiah Falls</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L165" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-24</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H166" t="str">
-        <v>PARTYOF2</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L166" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Dance In The USA</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-24</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G167" t="str">
-        <v>2:59</v>
+        <v>2:03</v>
       </c>
       <c r="H167" t="str">
-        <v>Show Me the Body</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L167" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tremolo</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-24</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G168" t="str">
-        <v>3:43</v>
+        <v>2:51</v>
       </c>
       <c r="H168" t="str">
-        <v>Metric</v>
+        <v>Montana 700</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L168" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>In the Dark</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-24</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The End is Not the End</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:52</v>
+        <v>2:31</v>
       </c>
       <c r="H169" t="str">
-        <v>Atreyu</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L169" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-24</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:36</v>
+        <v>3:28</v>
       </c>
       <c r="H170" t="str">
-        <v>Modest Mouse</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L170" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>I Saw Your Face</v>
+        <v>Twice</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-24</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G171" t="str">
-        <v>3:09</v>
+        <v>2:32</v>
       </c>
       <c r="H171" t="str">
-        <v>Malcolm Todd</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L171" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Demons In Your Choir</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-24</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Grateful</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:16</v>
+        <v>2:36</v>
       </c>
       <c r="H172" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L172" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Full Circle</v>
+        <v>hide and seek</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-24</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H173" t="str">
-        <v>Leonie Biney</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L173" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Be the One</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-24</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:39</v>
+        <v>3:25</v>
       </c>
       <c r="H174" t="str">
-        <v>Sophia Stel</v>
+        <v>Adam Port</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L174" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-24</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Destined For Greatness</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G175" t="str">
-        <v>2:03</v>
+        <v>4:46</v>
       </c>
       <c r="H175" t="str">
-        <v>Luh Tyler</v>
+        <v>Lane 8</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L175" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-24</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Sadetra Son</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:51</v>
+        <v>2:31</v>
       </c>
       <c r="H176" t="str">
-        <v>Montana 700</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L176" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Physical (feat. Kyozo)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/physical-feat-kyozo/1891816798</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-24</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Physical (feat. Kyozo) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:31</v>
+        <v>2:40</v>
       </c>
       <c r="H177" t="str">
-        <v>Thirteendegrees °</v>
+        <v>J. Worra</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/physical-feat-kyozo/1891816796</v>
       </c>
       <c r="L177" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Physical (feat. Kyozo) - J. Worra</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-24</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:28</v>
+        <v>3:19</v>
       </c>
       <c r="H178" t="str">
-        <v>Beach Bunny</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L178" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Twice</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-24</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:32</v>
+        <v>3:37</v>
       </c>
       <c r="H179" t="str">
-        <v>Arrows in Action</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L179" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Asleep Talking</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-24</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:36</v>
+        <v>3:04</v>
       </c>
       <c r="H180" t="str">
-        <v>Magnus Ferrell</v>
+        <v>FEYI</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L180" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>hide and seek</v>
+        <v>Campeones</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-24</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>hide and seek - Single</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:47</v>
+        <v>3:48</v>
       </c>
       <c r="H181" t="str">
-        <v>Hailey Picardi</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L181" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Be the One</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-24</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Be the One - Single</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G182" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H182" t="str">
-        <v>Adam Port</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L182" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>World Is Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-24</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>World Is Mine</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G183" t="str">
-        <v>4:46</v>
+        <v>2:41</v>
       </c>
       <c r="H183" t="str">
-        <v>Lane 8</v>
+        <v>Khatumu</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L183" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-24</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G184" t="str">
-        <v>2:31</v>
+        <v>3:37</v>
       </c>
       <c r="H184" t="str">
-        <v>Duke Dumont</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L184" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Physical (feat. Kyozo)</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/physical-feat-kyozo/1891816798</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-24</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Physical (feat. Kyozo) - Single</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G185" t="str">
-        <v>2:40</v>
+        <v>3:06</v>
       </c>
       <c r="H185" t="str">
-        <v>J. Worra</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/physical-feat-kyozo/1891816796</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L185" t="str">
-        <v>Physical (feat. Kyozo) - J. Worra</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-24</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G186" t="str">
-        <v>3:19</v>
+        <v>5:54</v>
       </c>
       <c r="H186" t="str">
-        <v>LEGADO 7</v>
+        <v>Friko</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L186" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>AM I OKAY?!</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-24</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:37</v>
+        <v>7:05</v>
       </c>
       <c r="H187" t="str">
-        <v>Durand Bernarr</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L187" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Have You Ever</v>
+        <v>Cake</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-24</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Have You Ever - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H188" t="str">
-        <v>FEYI</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L188" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Campeones</v>
+        <v>from a distance</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-24</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Campeones - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:48</v>
+        <v>2:47</v>
       </c>
       <c r="H189" t="str">
-        <v>Cypress Hill</v>
+        <v>Luz</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L189" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Second Hand</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-24</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:27</v>
+        <v>3:24</v>
       </c>
       <c r="H190" t="str">
-        <v>Mina Tindle</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L190" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>tennis practice</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-24</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G191" t="str">
-        <v>2:41</v>
+        <v>3:08</v>
       </c>
       <c r="H191" t="str">
-        <v>Khatumu</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L191" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Moon Not Mine</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-24</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Singing</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G192" t="str">
-        <v>3:37</v>
+        <v>2:40</v>
       </c>
       <c r="H192" t="str">
-        <v>Gia Margaret</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L192" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>You Say I Love You</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-24</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G193" t="str">
-        <v>3:06</v>
+        <v>3:50</v>
       </c>
       <c r="H193" t="str">
-        <v>Quiet Light</v>
+        <v>At The Gates</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L193" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-24</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>5:54</v>
+        <v>3:35</v>
       </c>
       <c r="H194" t="str">
-        <v>Friko</v>
+        <v>Sepultura</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L194" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Other Hells</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-24</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Other Hells - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>7:05</v>
+        <v>2:06</v>
       </c>
       <c r="H195" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Ceremony</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
       </c>
       <c r="L195" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Other Hells - Ceremony</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Cake</v>
+        <v>Hit a Moonshot</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-24</v>
@@ -7823,334 +7823,30 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Cake - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G196" t="str">
-        <v>2:36</v>
+        <v>4:34</v>
       </c>
       <c r="H196" t="str">
-        <v>Mila Smith</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
       <c r="L196" t="str">
-        <v>Cake - Mila Smith</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>from a distance</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>from a distance - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Luz</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
-      </c>
-      <c r="L197" t="str">
-        <v>from a distance - Luz</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Second Hand</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>Second Hand - Single</v>
-      </c>
-      <c r="G198" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Anais Cardot</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Second Hand - Anais Cardot</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Mnikeni</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Ku Ngawe</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:08</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Thando Zide</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Mnikeni - Thando Zide</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Lorcan's Song</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:40</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Christian Henson</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>In Dark Distortion</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>The Ghost of a Future Dead</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:50</v>
-      </c>
-      <c r="H201" t="str">
-        <v>At The Gates</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
-      </c>
-      <c r="L201" t="str">
-        <v>In Dark Distortion - At The Gates</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>All Souls Rising</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Sepultura</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
-      </c>
-      <c r="L202" t="str">
-        <v>All Souls Rising - Sepultura</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Other Hells</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Other Hells - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:06</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Ceremony</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Other Hells - Ceremony</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Hit a Moonshot</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G204" t="str">
-        <v>4:34</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
-      </c>
-      <c r="L204" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד – בית במושב</v>
+        <v>תהילה - מה שאני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%91%d7%99%d7%aa-%d7%91%d7%9e%d7%95%d7%a9%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410612&amp;sid=14abf7149976c01670080bda4e258547</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הטקסט של „"בית במושב” של יובל גולד עובד בדיוק על הקו שבין פשטות יומיומית לבין הצהרה רגשית עמוקה, בקצב שמשרת נרטיב אישי בבלדת רוק נוגה. השיר נשען על קצב יציב (כמעט “הליכה” רגועה), בלי שינויים דרמטיים: בינוני-איטי שיוצר תחושת אינטימיות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד – בית במושב</v>
+        <v>תהילה - מה שאני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410611&amp;sid=14abf7149976c01670080bda4e258547</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-24</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B4" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-24</v>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Danna</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-24</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-24</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-24</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Beck</v>
+        <v>Cannons</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-24</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Beck</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-24</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-24</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Digster Pop Music</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-24</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Beck</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B12" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-24</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>The All-American Rejects</v>
+        <v>Beck</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-24</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Armin van Buuren</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-24</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-24</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Madonna</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-24</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Freya Ridings</v>
+        <v>Madonna</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-24</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Celine Dion</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B18" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-24</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Peter Gabriel</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B19" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-24</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B20" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-24</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B21" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-24</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-24</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>ERNEST</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-24</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>ERNEST</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-24</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-24</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-24</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Kip Moore</v>
+        <v>Bella White</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B27" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-24</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-24</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Ben Gallaher</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-24</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-24</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Johnny Orlando</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-24</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Tyla</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-24</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Tyla</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-24</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lana Del Rey</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-24</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Loreen</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-24</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Loreen</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-24</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Tenille Townes</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-24</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B38" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-24</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Danna</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-24</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>OneRepublic</v>
+        <v>Danna</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-24</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>The Revivalists</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-24</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>James Smith</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-24</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Holly Humberstone</v>
+        <v>James Smith</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-24</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-24</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-24</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-24</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>Ava Max</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B47" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-24</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Conan Gray</v>
+        <v>Danna</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-24</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>TemplesOfficial</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-24</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Laufey</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-24</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>bleachers</v>
+        <v>Laufey</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-24</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>bleachers</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B52" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-24</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>LANY</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-24</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>LANY</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B54" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-24</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-24</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-24</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Kygo and carter faith</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-24</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>florencemachine</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-24</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Scorpions</v>
+        <v>florencemachine</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-24</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-24</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-24</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-24</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-24</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Mae Muller</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-24</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Dead Pony</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-24</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-24</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>kenzie - where do we go</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-24</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>kenzie</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-24</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Foo Fighters</v>
+        <v>kenzie</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-24</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Laufey</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-24</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>Laufey</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-24</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mei Semones</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-24</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Evanescence</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-24</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>elijah woods</v>
+        <v>Evanescence</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-24</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>colby!</v>
+        <v>elijah woods</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-24</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Chainsmokers</v>
+        <v>colby!</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-24</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>aron!</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-24</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Owen Riegling</v>
+        <v>aron!</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-24</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-24</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Teddy Swims</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-24</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-24</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-24</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Sunday (1994)</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-24</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-24</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Freya Skye</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-24</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Bryan Adams</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-24</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>We Three</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-24</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Dermot Kennedy</v>
+        <v>We Three</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-24</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Bebe Rexha</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-24</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-24</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>METTE</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-24</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Saint Harison</v>
+        <v>METTE</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-24</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>NewDad</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-24</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Danna</v>
+        <v>NewDad</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-24</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>florencemachine</v>
+        <v>Danna</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-24</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>HYBE LABELS</v>
+        <v>florencemachine</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-24</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Kungs</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-24</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Charlie Puth</v>
+        <v>Kungs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-24</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-24</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-24</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Madison Cunningham</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-24</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B102" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-24</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-24</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kehlani</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Kehlani</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Después de ti</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-24</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Después de ti - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G104" t="str">
-        <v>4:35</v>
+        <v>3:06</v>
       </c>
       <c r="H104" t="str">
-        <v>KAROL G</v>
+        <v>Kehlani</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L104" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dando Vueltas</v>
+        <v>Después de ti</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-24</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:12</v>
+        <v>4:35</v>
       </c>
       <c r="H105" t="str">
-        <v>Rauw Alejandro</v>
+        <v>KAROL G</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L105" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Doors</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-24</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:51</v>
+        <v>3:12</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L106" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>Doors</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-24</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G107" t="str">
-        <v>3:48</v>
+        <v>3:51</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Langley</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L107" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Todos nos Shipean</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-24</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:16</v>
+        <v>3:48</v>
       </c>
       <c r="H108" t="str">
-        <v>Fuerza Regida</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L108" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Ojitos Bellos</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-24</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:59</v>
+        <v>2:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Grupo Frontera</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L109" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>REDRED</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-24</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>2:59</v>
       </c>
       <c r="H110" t="str">
-        <v>CORTIS</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L110" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Little More Time</v>
+        <v>REDRED</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-24</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dinner Party</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G111" t="str">
-        <v>3:38</v>
+        <v>2:43</v>
       </c>
       <c r="H111" t="str">
-        <v>Niall Horan</v>
+        <v>CORTIS</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L111" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>earth is turning</v>
+        <v>Little More Time</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-24</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G112" t="str">
-        <v>4:49</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>horsegiirL</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L112" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Better</v>
+        <v>earth is turning</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-24</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>U</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G113" t="str">
-        <v>3:50</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Baauer</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L113" t="str">
-        <v>Better - Baauer</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Ride Lonesome</v>
+        <v>Better</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-24</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>U</v>
       </c>
       <c r="G114" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H114" t="str">
-        <v>Beck</v>
+        <v>Baauer</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L114" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-24</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>1:56</v>
+        <v>4:32</v>
       </c>
       <c r="H115" t="str">
-        <v>Billie Eilish</v>
+        <v>Beck</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L115" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-24</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Big Mama</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:29</v>
+        <v>1:56</v>
       </c>
       <c r="H116" t="str">
-        <v>Latto</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L116" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Born To Die</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-24</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Born To Die - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G117" t="str">
-        <v>2:45</v>
+        <v>2:29</v>
       </c>
       <c r="H117" t="str">
-        <v>Shaboozey</v>
+        <v>Latto</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L117" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-24</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Florescence</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H118" t="str">
-        <v>Maisie Peters</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L118" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Tiny Raisin</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-24</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Loveland</v>
+        <v>Florescence</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L119" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Fantasy</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-24</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Loveland</v>
       </c>
       <c r="G120" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H120" t="str">
-        <v>Demi Lovato</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L120" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Already Know</v>
+        <v>Fantasy</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-24</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G121" t="str">
-        <v>2:37</v>
+        <v>2:21</v>
       </c>
       <c r="H121" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L121" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>PIECES</v>
+        <v>Already Know</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-24</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>3:25</v>
+        <v>2:37</v>
       </c>
       <c r="H122" t="str">
-        <v>The Kid LAROI</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L122" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Shimmer</v>
+        <v>PIECES</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-24</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Toy With Me</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H123" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L123" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Window</v>
+        <v>Shimmer</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-24</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G124" t="str">
-        <v>3:37</v>
+        <v>2:47</v>
       </c>
       <c r="H124" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L124" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Reward the Scars</v>
+        <v>Window</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-24</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G125" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H125" t="str">
-        <v>Korn</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L125" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-24</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H126" t="str">
-        <v>Jason Aldean</v>
+        <v>Korn</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L126" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>La Buena</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-24</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>La Buena - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G127" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Carín León</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L127" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>You Better Know</v>
+        <v>La Buena</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-24</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Ebony Riley</v>
+        <v>Carín León</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L128" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Planting Tomatoes</v>
+        <v>You Better Know</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-24</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G129" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H129" t="str">
-        <v>Lucy Dacus</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L129" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Back of a Truck</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-24</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>American Stories</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:00</v>
+        <v>3:35</v>
       </c>
       <c r="H130" t="str">
-        <v>Rostam</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L130" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>FIX UR FACE</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-24</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G131" t="str">
-        <v>3:19</v>
+        <v>4:00</v>
       </c>
       <c r="H131" t="str">
-        <v>mgk</v>
+        <v>Rostam</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L131" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>CELEBRATION</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-24</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H132" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L132" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Door</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-24</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Conan Gray</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L133" t="str">
-        <v>Door - Conan Gray</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Hate Myself</v>
+        <v>Door</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-24</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G134" t="str">
-        <v>2:32</v>
+        <v>3:54</v>
       </c>
       <c r="H134" t="str">
-        <v>Ruel</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L134" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>DREAMBOY</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-24</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H135" t="str">
-        <v>MICO</v>
+        <v>Ruel</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L135" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-24</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Daniel Seavey</v>
+        <v>MICO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L136" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-24</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H137" t="str">
-        <v>The Two Lips</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L137" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>car crash</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-24</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>car crash - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:40</v>
+        <v>3:23</v>
       </c>
       <c r="H138" t="str">
-        <v>jigitz</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L138" t="str">
-        <v>car crash - jigitz</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>All This Disaster</v>
+        <v>car crash</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-24</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>All This Disaster - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:22</v>
+        <v>2:40</v>
       </c>
       <c r="H139" t="str">
-        <v>Sarah McLachlan</v>
+        <v>jigitz</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L139" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Better Days</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-24</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H140" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L140" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>The Rising Skyline</v>
+        <v>Better Days</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-24</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Location Lost</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G141" t="str">
-        <v>4:32</v>
+        <v>3:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Failure</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L141" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Cryogen</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-24</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Wow! Signal</v>
+        <v>Location Lost</v>
       </c>
       <c r="G142" t="str">
-        <v>5:01</v>
+        <v>4:32</v>
       </c>
       <c r="H142" t="str">
-        <v>Muse</v>
+        <v>Failure</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L142" t="str">
-        <v>Cryogen - Muse</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Cryogen</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-24</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G143" t="str">
-        <v>1:21</v>
+        <v>5:01</v>
       </c>
       <c r="H143" t="str">
-        <v>Nick Cave</v>
+        <v>Muse</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L143" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-24</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G144" t="str">
-        <v>3:39</v>
+        <v>1:21</v>
       </c>
       <c r="H144" t="str">
-        <v>Genesis Owusu</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L144" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>HBO</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-24</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>HBO - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G145" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H145" t="str">
-        <v>Yung Gravy</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L145" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Need For Speed</v>
+        <v>HBO</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-24</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Need For Speed - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:15</v>
+        <v>3:42</v>
       </c>
       <c r="H146" t="str">
-        <v>Kim Petras</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L146" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>collide</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-24</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H147" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L147" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>freak for you</v>
+        <v>collide</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-24</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>freak for you - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G148" t="str">
-        <v>2:26</v>
+        <v>3:43</v>
       </c>
       <c r="H148" t="str">
-        <v>Haiden Henderson</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L148" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Anymore</v>
+        <v>freak for you</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-24</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H149" t="str">
-        <v>Asha Banks</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L149" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Why Am I Here</v>
+        <v>Anymore</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-24</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:17</v>
+        <v>2:37</v>
       </c>
       <c r="H150" t="str">
-        <v>Presley Regier</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L150" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>oh child</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-24</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>oh child - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>2:02</v>
+        <v>3:17</v>
       </c>
       <c r="H151" t="str">
-        <v>kai devega</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L151" t="str">
-        <v>oh child - kai devega</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Dance To This</v>
+        <v>oh child</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-24</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Ritual</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:54</v>
+        <v>2:02</v>
       </c>
       <c r="H152" t="str">
-        <v>Icona Pop</v>
+        <v>kai devega</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L152" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Dance To This</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-24</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G153" t="str">
-        <v>3:58</v>
+        <v>2:54</v>
       </c>
       <c r="H153" t="str">
-        <v>Tauren Wells</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L153" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>You Can Have Him</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-24</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:15</v>
+        <v>3:58</v>
       </c>
       <c r="H154" t="str">
-        <v>Carly Pearce</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L154" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Backwards</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-24</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Backwards - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H155" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L155" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Backwards</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-24</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Serial Romantic</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H156" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L156" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-24</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G157" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H157" t="str">
-        <v>Isaiah Falls</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L157" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-24</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:42</v>
+        <v>3:43</v>
       </c>
       <c r="H158" t="str">
-        <v>PARTYOF2</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L158" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Dance In The USA</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-24</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H159" t="str">
-        <v>Show Me the Body</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L159" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Tremolo</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-24</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H160" t="str">
-        <v>Metric</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L160" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>In the Dark</v>
+        <v>Tremolo</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-24</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>The End is Not the End</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G161" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H161" t="str">
-        <v>Atreyu</v>
+        <v>Metric</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L161" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>In the Dark</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-24</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G162" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H162" t="str">
-        <v>Modest Mouse</v>
+        <v>Atreyu</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L162" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Saw Your Face</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-24</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G163" t="str">
-        <v>3:09</v>
+        <v>4:36</v>
       </c>
       <c r="H163" t="str">
-        <v>Malcolm Todd</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L163" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Demons In Your Choir</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-24</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Grateful</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:16</v>
+        <v>3:09</v>
       </c>
       <c r="H164" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L164" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Full Circle</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-24</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Grateful</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H165" t="str">
-        <v>Leonie Biney</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L165" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-24</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>3:39</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Sophia Stel</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L166" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-24</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Destined For Greatness</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:03</v>
+        <v>3:39</v>
       </c>
       <c r="H167" t="str">
-        <v>Luh Tyler</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L167" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-24</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Sadetra Son</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G168" t="str">
-        <v>2:51</v>
+        <v>2:03</v>
       </c>
       <c r="H168" t="str">
-        <v>Montana 700</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L168" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-24</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G169" t="str">
-        <v>2:31</v>
+        <v>2:51</v>
       </c>
       <c r="H169" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Montana 700</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L169" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-24</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:28</v>
+        <v>2:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Beach Bunny</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L170" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Twice</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-24</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:32</v>
+        <v>3:28</v>
       </c>
       <c r="H171" t="str">
-        <v>Arrows in Action</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L171" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Asleep Talking</v>
+        <v>Twice</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-24</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G172" t="str">
-        <v>2:36</v>
+        <v>2:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L172" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>hide and seek</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-24</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>hide and seek - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H173" t="str">
-        <v>Hailey Picardi</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L173" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Be the One</v>
+        <v>hide and seek</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-24</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Be the One - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H174" t="str">
-        <v>Adam Port</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L174" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-24</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:46</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Lane 8</v>
+        <v>Adam Port</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L175" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-24</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G176" t="str">
-        <v>2:31</v>
+        <v>4:46</v>
       </c>
       <c r="H176" t="str">
-        <v>Duke Dumont</v>
+        <v>Lane 8</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L176" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Physical (feat. Kyozo)</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/physical-feat-kyozo/1891816798</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-24</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Physical (feat. Kyozo) - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:40</v>
+        <v>2:31</v>
       </c>
       <c r="H177" t="str">
-        <v>J. Worra</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/physical-feat-kyozo/1891816796</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L177" t="str">
-        <v>Physical (feat. Kyozo) - J. Worra</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Physical (feat. Kyozo)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/physical-feat-kyozo/1891816798</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-24</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Physical (feat. Kyozo) - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H178" t="str">
-        <v>LEGADO 7</v>
+        <v>J. Worra</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/physical-feat-kyozo/1891816796</v>
       </c>
       <c r="L178" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Physical (feat. Kyozo) - J. Worra</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>AM I OKAY?!</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-24</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Durand Bernarr</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L179" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Have You Ever</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-24</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Have You Ever - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H180" t="str">
-        <v>FEYI</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L180" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Campeones</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-24</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Campeones - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H181" t="str">
-        <v>Cypress Hill</v>
+        <v>FEYI</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L181" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Campeones</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-24</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:27</v>
+        <v>3:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Mina Tindle</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L182" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>tennis practice</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-24</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G183" t="str">
-        <v>2:41</v>
+        <v>3:27</v>
       </c>
       <c r="H183" t="str">
-        <v>Khatumu</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L183" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Moon Not Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-24</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Singing</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:37</v>
+        <v>2:41</v>
       </c>
       <c r="H184" t="str">
-        <v>Gia Margaret</v>
+        <v>Khatumu</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L184" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>You Say I Love You</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-24</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Singing</v>
       </c>
       <c r="G185" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H185" t="str">
-        <v>Quiet Light</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L185" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-24</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G186" t="str">
-        <v>5:54</v>
+        <v>3:06</v>
       </c>
       <c r="H186" t="str">
-        <v>Friko</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L186" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-24</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G187" t="str">
-        <v>7:05</v>
+        <v>5:54</v>
       </c>
       <c r="H187" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Friko</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L187" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Cake</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-24</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Cake - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>2:36</v>
+        <v>7:05</v>
       </c>
       <c r="H188" t="str">
-        <v>Mila Smith</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L188" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>from a distance</v>
+        <v>Cake</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-24</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>from a distance - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H189" t="str">
-        <v>Luz</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L189" t="str">
-        <v>from a distance - Luz</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Second Hand</v>
+        <v>from a distance</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-24</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Second Hand - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H190" t="str">
-        <v>Anais Cardot</v>
+        <v>Luz</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L190" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Mnikeni</v>
+        <v>Second Hand</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-24</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ku Ngawe</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H191" t="str">
-        <v>Thando Zide</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L191" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Lorcan's Song</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-24</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G192" t="str">
-        <v>2:40</v>
+        <v>3:08</v>
       </c>
       <c r="H192" t="str">
-        <v>Christian Henson</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L192" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>In Dark Distortion</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-24</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G193" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H193" t="str">
-        <v>At The Gates</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L193" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>All Souls Rising</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-24</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G194" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H194" t="str">
-        <v>Sepultura</v>
+        <v>At The Gates</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L194" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Other Hells</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-24</v>
@@ -7785,68 +7785,106 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Other Hells - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>2:06</v>
+        <v>3:35</v>
       </c>
       <c r="H195" t="str">
-        <v>Ceremony</v>
+        <v>Sepultura</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L195" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D196" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
+      <c r="D197" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G196" t="str">
+      <c r="G197" t="str">
         <v>4:34</v>
       </c>
-      <c r="H196" t="str">
+      <c r="H197" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K196" t="str">
+      <c r="K197" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L196" t="str">
+      <c r="L197" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week04/titles.xlsx
+++ b/data/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהילה - מה שאני</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410612&amp;sid=14abf7149976c01670080bda4e258547</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-24</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהילה - מה שאני</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-24</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410611&amp;sid=14abf7149976c01670080bda4e258547</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-24</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-24</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Danna</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-24</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Cannons</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-24</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Beck</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-24</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Cannons</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-24</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Beck</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-24</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-24</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Beck</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-24</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Digster Pop Music</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-24</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Beck</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-24</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>The All-American Rejects</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-24</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madonna</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-24</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Demi Lovato</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-24</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Madonna</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-24</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Freya Ridings</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-24</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Celine Dion</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-24</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-24</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-24</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Jessie Ware</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-24</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>The Kid LAROI.</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-24</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>ERNEST</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-24</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Bella White</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-24</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-24</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Bella White</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-24</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Kip Moore</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-24</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-24</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Ben Gallaher</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-24</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Tyla</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-24</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Johnny Orlando</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-24</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Tyla</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-24</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Loreen</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-24</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Lana Del Rey</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-24</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Loreen</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-24</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-24</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Tenille Townes</v>
+        <v>Danna</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-24</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-24</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Danna</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-24</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>OneRepublic</v>
+        <v>James Smith</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-24</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>The Revivalists</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-24</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>James Smith</v>
+        <v>Ava Max</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-24</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Holly Humberstone</v>
+        <v>John Summit</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-24</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-24</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>John Summit</v>
+        <v>Danna</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-24</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Ava Max</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-24</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Danna</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-24</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Conan Gray</v>
+        <v>Laufey</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-24</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>TemplesOfficial</v>
+        <v>bleachers</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-24</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-24</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>bleachers</v>
+        <v>LANY</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-24</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-24</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>LANY</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-24</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-24</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-24</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>florencemachine</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-24</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Scorpions</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+   